--- a/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Validasi\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F3F3310-9467-408F-AA46-6D48354A64B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -237,8 +243,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,13 +307,1540 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A*</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>7.7780000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.8300000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0164300000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.34176450000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BDS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$3:$F$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.6190000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.8489999999999992E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7950000000000011E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6024400000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>BRC</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$4:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3.812000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.2056E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.8049E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.3635400000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>GL</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.2050000000000007E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6591999999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.3972500000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16289010000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>JPS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.4199999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2631000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0398000000000015E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3102199999999998E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PPO</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8.2840000000000019E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.8693E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.01517E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.34366750000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TPF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Waktu Pencarian'!$C$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Waktu Pencarian'!$C$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.0001000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.9628000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.1960399999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.34526259999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-5D0F-4C3B-9C4D-4EDE8373BA79}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1087434447"/>
+        <c:axId val="1087424847"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1087434447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087424847"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1087424847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="id-ID"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="id-ID"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1087434447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="id-ID"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="id-ID"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5ED12D6-EDF7-B5CF-57F4-9F6E8B755A02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -345,7 +1878,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -379,6 +1912,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -413,9 +1947,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,11 +2123,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +2150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -623,22 +2158,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.0007778</v>
+        <v>7.7780000000000004E-4</v>
       </c>
       <c r="D2">
-        <v>0.00583</v>
+        <v>5.8300000000000001E-3</v>
       </c>
       <c r="E2">
-        <v>0.0501643</v>
+        <v>5.0164300000000002E-2</v>
       </c>
       <c r="F2">
-        <v>0.3417645</v>
+        <v>0.34176450000000003</v>
       </c>
       <c r="G2">
-        <v>0.09963415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>9.9634150000000005E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -646,22 +2181,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.0002619</v>
+        <v>2.6190000000000002E-4</v>
       </c>
       <c r="D3">
-        <v>0.0009848999999999999</v>
+        <v>9.8489999999999992E-4</v>
       </c>
       <c r="E3">
-        <v>0.003795000000000001</v>
+        <v>3.7950000000000011E-3</v>
       </c>
       <c r="F3">
-        <v>0.0160244</v>
+        <v>1.6024400000000001E-2</v>
       </c>
       <c r="G3">
-        <v>0.00526655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>5.2665500000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -669,22 +2204,22 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.0003812000000000001</v>
+        <v>3.812000000000001E-4</v>
       </c>
       <c r="D4">
-        <v>0.0012056</v>
+        <v>1.2056E-3</v>
       </c>
       <c r="E4">
-        <v>0.0048049</v>
+        <v>4.8049E-3</v>
       </c>
       <c r="F4">
-        <v>0.0236354</v>
+        <v>2.3635400000000001E-2</v>
       </c>
       <c r="G4">
-        <v>0.007506775</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>7.5067750000000003E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -692,22 +2227,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.0006205000000000001</v>
+        <v>6.2050000000000007E-4</v>
       </c>
       <c r="D5">
-        <v>0.003659199999999999</v>
+        <v>3.6591999999999992E-3</v>
       </c>
       <c r="E5">
-        <v>0.0239725</v>
+        <v>2.3972500000000001E-2</v>
       </c>
       <c r="F5">
-        <v>0.1628901</v>
+        <v>0.16289010000000001</v>
       </c>
       <c r="G5">
-        <v>0.047785575</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>4.7785574999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -715,22 +2250,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>0.000642</v>
+        <v>6.4199999999999999E-4</v>
       </c>
       <c r="D6">
-        <v>0.0022631</v>
+        <v>2.2631000000000001E-3</v>
       </c>
       <c r="E6">
-        <v>0.008039800000000001</v>
+        <v>8.0398000000000015E-3</v>
       </c>
       <c r="F6">
-        <v>0.0331022</v>
+        <v>3.3102199999999998E-2</v>
       </c>
       <c r="G6">
-        <v>0.011011775</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>1.1011775E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -738,22 +2273,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>0.0008284000000000002</v>
+        <v>8.2840000000000019E-4</v>
       </c>
       <c r="D7">
-        <v>0.0058693</v>
+        <v>5.8693E-3</v>
       </c>
       <c r="E7">
-        <v>0.0501517</v>
+        <v>5.01517E-2</v>
       </c>
       <c r="F7">
-        <v>0.3436675</v>
+        <v>0.34366750000000001</v>
       </c>
       <c r="G7">
         <v>0.100129225</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -761,22 +2296,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.0010001</v>
+        <v>1.0001000000000001E-3</v>
       </c>
       <c r="D8">
-        <v>0.006962800000000001</v>
+        <v>6.9628000000000008E-3</v>
       </c>
       <c r="E8">
-        <v>0.0519604</v>
+        <v>5.1960399999999997E-2</v>
       </c>
       <c r="F8">
-        <v>0.3452626</v>
+        <v>0.34526259999999998</v>
       </c>
       <c r="G8">
         <v>0.101296475</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -784,22 +2319,22 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>0.000401</v>
+        <v>4.0099999999999999E-4</v>
       </c>
       <c r="D9">
-        <v>0.0010075</v>
+        <v>1.0074999999999999E-3</v>
       </c>
       <c r="E9">
-        <v>0.0025002</v>
+        <v>2.5002000000000002E-3</v>
       </c>
       <c r="F9">
-        <v>0.007648200000000001</v>
+        <v>7.6482000000000008E-3</v>
       </c>
       <c r="G9">
-        <v>0.002889225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>2.889225E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -807,22 +2342,22 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>0.0003341</v>
+        <v>3.3409999999999999E-4</v>
       </c>
       <c r="D10">
-        <v>0.0013165</v>
+        <v>1.3165E-3</v>
       </c>
       <c r="E10">
-        <v>0.005200600000000001</v>
+        <v>5.2006000000000014E-3</v>
       </c>
       <c r="F10">
-        <v>0.0220319</v>
+        <v>2.20319E-2</v>
       </c>
       <c r="G10">
-        <v>0.007220775</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>7.2207749999999996E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -830,22 +2365,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.0003074</v>
+        <v>3.0739999999999999E-4</v>
       </c>
       <c r="D11">
-        <v>0.0011617</v>
+        <v>1.1617000000000001E-3</v>
       </c>
       <c r="E11">
-        <v>0.004092699999999999</v>
+        <v>4.0926999999999986E-3</v>
       </c>
       <c r="F11">
-        <v>0.017126</v>
+        <v>1.7125999999999999E-2</v>
       </c>
       <c r="G11">
-        <v>0.005671949999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>5.6719499999999994E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -853,22 +2388,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>0.0003516999999999999</v>
+        <v>3.5169999999999988E-4</v>
       </c>
       <c r="D12">
-        <v>0.0011149</v>
+        <v>1.1149E-3</v>
       </c>
       <c r="E12">
-        <v>0.004308500000000001</v>
+        <v>4.3085000000000007E-3</v>
       </c>
       <c r="F12">
-        <v>0.0164408</v>
+        <v>1.6440799999999998E-2</v>
       </c>
       <c r="G12">
-        <v>0.005553975000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>5.5539750000000009E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -876,22 +2411,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.0004306</v>
+        <v>4.306E-4</v>
       </c>
       <c r="D13">
-        <v>0.0013179</v>
+        <v>1.3179000000000001E-3</v>
       </c>
       <c r="E13">
-        <v>0.0050933</v>
+        <v>5.0933000000000003E-3</v>
       </c>
       <c r="F13">
-        <v>0.0248216</v>
+        <v>2.4821599999999999E-2</v>
       </c>
       <c r="G13">
-        <v>0.00791585</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>7.9158500000000003E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -899,22 +2434,22 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>0.0004580999999999999</v>
+        <v>4.5809999999999991E-4</v>
       </c>
       <c r="D14">
-        <v>0.0013389</v>
+        <v>1.3389000000000001E-3</v>
       </c>
       <c r="E14">
-        <v>0.0048674</v>
+        <v>4.8674E-3</v>
       </c>
       <c r="F14">
-        <v>0.0224073</v>
+        <v>2.2407300000000002E-2</v>
       </c>
       <c r="G14">
-        <v>0.007267925000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>7.2679250000000006E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -922,22 +2457,22 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>0.0006663000000000001</v>
+        <v>6.663000000000001E-4</v>
       </c>
       <c r="D15">
-        <v>0.0024359</v>
+        <v>2.4359E-3</v>
       </c>
       <c r="E15">
-        <v>0.0116133</v>
+        <v>1.16133E-2</v>
       </c>
       <c r="F15">
-        <v>0.0675756</v>
+        <v>6.75756E-2</v>
       </c>
       <c r="G15">
-        <v>0.020572775</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>2.0572775000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -945,22 +2480,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>0.0006510999999999999</v>
+        <v>6.5109999999999994E-4</v>
       </c>
       <c r="D16">
-        <v>0.0037637</v>
+        <v>3.7637E-3</v>
       </c>
       <c r="E16">
-        <v>0.0242281</v>
+        <v>2.4228099999999999E-2</v>
       </c>
       <c r="F16">
-        <v>0.1640695</v>
+        <v>0.16406950000000001</v>
       </c>
       <c r="G16">
-        <v>0.0481781</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>4.8178100000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -968,22 +2503,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>0.0005857</v>
+        <v>5.8569999999999998E-4</v>
       </c>
       <c r="D17">
-        <v>0.0032192</v>
+        <v>3.2192000000000002E-3</v>
       </c>
       <c r="E17">
-        <v>0.0202813</v>
+        <v>2.0281299999999999E-2</v>
       </c>
       <c r="F17">
-        <v>0.1554357</v>
+        <v>0.15543570000000001</v>
       </c>
       <c r="G17">
-        <v>0.044880475</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>4.4880475000000003E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -991,22 +2526,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.0004311</v>
+        <v>4.3110000000000002E-4</v>
       </c>
       <c r="D18">
-        <v>0.0016268</v>
+        <v>1.6268000000000001E-3</v>
       </c>
       <c r="E18">
-        <v>0.0060882</v>
+        <v>6.0882000000000002E-3</v>
       </c>
       <c r="F18">
-        <v>0.0236955</v>
+        <v>2.3695500000000001E-2</v>
       </c>
       <c r="G18">
-        <v>0.007960399999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>7.9603999999999994E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1014,22 +2549,22 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>0.0003523</v>
+        <v>3.523E-4</v>
       </c>
       <c r="D19">
-        <v>0.0010477</v>
+        <v>1.0476999999999999E-3</v>
       </c>
       <c r="E19">
-        <v>0.0037186</v>
+        <v>3.7185999999999999E-3</v>
       </c>
       <c r="F19">
-        <v>0.0167977</v>
+        <v>1.6797699999999999E-2</v>
       </c>
       <c r="G19">
-        <v>0.005479075000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>5.4790750000000008E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -1037,22 +2572,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0.0005379</v>
+        <v>5.3790000000000001E-4</v>
       </c>
       <c r="D20">
-        <v>0.0018773</v>
+        <v>1.8772999999999999E-3</v>
       </c>
       <c r="E20">
-        <v>0.0065545</v>
+        <v>6.5545000000000004E-3</v>
       </c>
       <c r="F20">
-        <v>0.0251948</v>
+        <v>2.51948E-2</v>
       </c>
       <c r="G20">
-        <v>0.008541125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>8.5411250000000001E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -1060,22 +2595,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>0.0006656</v>
+        <v>6.6560000000000002E-4</v>
       </c>
       <c r="D21">
-        <v>0.002819700000000001</v>
+        <v>2.8197000000000009E-3</v>
       </c>
       <c r="E21">
-        <v>0.008114100000000001</v>
+        <v>8.1141000000000008E-3</v>
       </c>
       <c r="F21">
-        <v>0.0331979</v>
+        <v>3.3197900000000002E-2</v>
       </c>
       <c r="G21">
-        <v>0.011199325</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>1.1199325E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1083,22 +2618,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>0.0006387000000000001</v>
+        <v>6.3870000000000007E-4</v>
       </c>
       <c r="D22">
-        <v>0.0027457</v>
+        <v>2.7456999999999998E-3</v>
       </c>
       <c r="E22">
-        <v>0.007746099999999999</v>
+        <v>7.7460999999999988E-3</v>
       </c>
       <c r="F22">
-        <v>0.03201060000000001</v>
+        <v>3.2010600000000007E-2</v>
       </c>
       <c r="G22">
-        <v>0.010785275</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>1.0785275E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -1106,22 +2641,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>0.0010258</v>
+        <v>1.0258000000000001E-3</v>
       </c>
       <c r="D23">
-        <v>0.007072299999999999</v>
+        <v>7.0722999999999992E-3</v>
       </c>
       <c r="E23">
-        <v>0.05150780000000001</v>
+        <v>5.1507800000000013E-2</v>
       </c>
       <c r="F23">
-        <v>0.3459387</v>
+        <v>0.34593869999999999</v>
       </c>
       <c r="G23">
-        <v>0.10138615</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>0.10138614999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1129,22 +2664,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>0.0004445</v>
+        <v>4.4450000000000002E-4</v>
       </c>
       <c r="D24">
-        <v>0.0010833</v>
+        <v>1.0832999999999999E-3</v>
       </c>
       <c r="E24">
-        <v>0.0028127</v>
+        <v>2.8127E-3</v>
       </c>
       <c r="F24">
-        <v>0.0085314</v>
+        <v>8.5313999999999997E-3</v>
       </c>
       <c r="G24">
-        <v>0.003217975</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>3.2179750000000001E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1152,22 +2687,22 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>0.0004292</v>
+        <v>4.2920000000000002E-4</v>
       </c>
       <c r="D25">
-        <v>0.0010694</v>
+        <v>1.0694000000000001E-3</v>
       </c>
       <c r="E25">
-        <v>0.0025151</v>
+        <v>2.5151000000000001E-3</v>
       </c>
       <c r="F25">
-        <v>0.0074463</v>
+        <v>7.4463000000000003E-3</v>
       </c>
       <c r="G25">
-        <v>0.002865</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>2.8649999999999999E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -1175,22 +2710,22 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>0.000687</v>
+        <v>6.87E-4</v>
       </c>
       <c r="D26">
-        <v>0.0022269</v>
+        <v>2.2269E-3</v>
       </c>
       <c r="E26">
-        <v>0.008003199999999999</v>
+        <v>8.0031999999999985E-3</v>
       </c>
       <c r="F26">
-        <v>0.0344952</v>
+        <v>3.4495199999999997E-2</v>
       </c>
       <c r="G26">
-        <v>0.011353075</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1.1353075000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1198,22 +2733,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0003971000000000001</v>
+        <v>3.9710000000000011E-4</v>
       </c>
       <c r="D27">
-        <v>0.001496</v>
+        <v>1.4959999999999999E-3</v>
       </c>
       <c r="E27">
-        <v>0.0055835</v>
+        <v>5.5834999999999999E-3</v>
       </c>
       <c r="F27">
-        <v>0.0233959</v>
+        <v>2.3395900000000001E-2</v>
       </c>
       <c r="G27">
-        <v>0.007718125</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>7.7181250000000002E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -1221,22 +2756,22 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>0.0003496</v>
+        <v>3.4959999999999999E-4</v>
       </c>
       <c r="D28">
-        <v>0.0014883</v>
+        <v>1.4882999999999999E-3</v>
       </c>
       <c r="E28">
-        <v>0.0054782</v>
+        <v>5.4781999999999999E-3</v>
       </c>
       <c r="F28">
-        <v>0.0228348</v>
+        <v>2.2834799999999999E-2</v>
       </c>
       <c r="G28">
-        <v>0.007537725</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>7.5377250000000003E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -1244,22 +2779,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>0.000404</v>
+        <v>4.0400000000000001E-4</v>
       </c>
       <c r="D29">
-        <v>0.0012386</v>
+        <v>1.2386000000000001E-3</v>
       </c>
       <c r="E29">
-        <v>0.0046185</v>
+        <v>4.6185000000000002E-3</v>
       </c>
       <c r="F29">
-        <v>0.017524</v>
+        <v>1.7524000000000001E-2</v>
       </c>
       <c r="G29">
-        <v>0.005946274999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>5.9462749999999991E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -1267,22 +2802,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>0.0004976000000000001</v>
+        <v>4.9760000000000006E-4</v>
       </c>
       <c r="D30">
-        <v>0.0014816</v>
+        <v>1.4816E-3</v>
       </c>
       <c r="E30">
-        <v>0.005159200000000001</v>
+        <v>5.1592000000000009E-3</v>
       </c>
       <c r="F30">
-        <v>0.0237207</v>
+        <v>2.3720700000000001E-2</v>
       </c>
       <c r="G30">
-        <v>0.007714775</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>7.7147750000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -1290,22 +2825,22 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>0.0006967</v>
+        <v>6.9669999999999997E-4</v>
       </c>
       <c r="D31">
-        <v>0.0025982</v>
+        <v>2.5982000000000002E-3</v>
       </c>
       <c r="E31">
-        <v>0.0120979</v>
+        <v>1.20979E-2</v>
       </c>
       <c r="F31">
-        <v>0.06860699999999999</v>
+        <v>6.8606999999999987E-2</v>
       </c>
       <c r="G31">
-        <v>0.02099995</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>2.099995E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -1313,22 +2848,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>0.0007064999999999999</v>
+        <v>7.0649999999999988E-4</v>
       </c>
       <c r="D32">
-        <v>0.0014011</v>
+        <v>1.4011E-3</v>
       </c>
       <c r="E32">
-        <v>0.005958199999999999</v>
+        <v>5.9581999999999986E-3</v>
       </c>
       <c r="F32">
-        <v>0.0609615</v>
+        <v>6.0961500000000002E-2</v>
       </c>
       <c r="G32">
-        <v>0.017256825</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>1.7256825E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -1336,22 +2871,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>0.0006578999999999999</v>
+        <v>6.5789999999999989E-4</v>
       </c>
       <c r="D33">
-        <v>0.0033947</v>
+        <v>3.3947000000000001E-3</v>
       </c>
       <c r="E33">
-        <v>0.0204543</v>
+        <v>2.0454300000000002E-2</v>
       </c>
       <c r="F33">
-        <v>0.1546325</v>
+        <v>0.15463250000000001</v>
       </c>
       <c r="G33">
-        <v>0.04478485</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>4.4784850000000001E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -1359,22 +2894,22 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>0.0004718</v>
+        <v>4.7179999999999998E-4</v>
       </c>
       <c r="D34">
-        <v>0.0020597</v>
+        <v>2.0596999999999998E-3</v>
       </c>
       <c r="E34">
-        <v>0.0064759</v>
+        <v>6.4758999999999997E-3</v>
       </c>
       <c r="F34">
-        <v>0.0253361</v>
+        <v>2.53361E-2</v>
       </c>
       <c r="G34">
-        <v>0.008585875</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>8.5858749999999998E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -1382,22 +2917,22 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.0004967</v>
+        <v>4.9669999999999998E-4</v>
       </c>
       <c r="D35">
-        <v>0.0020319</v>
+        <v>2.0319000000000001E-3</v>
       </c>
       <c r="E35">
-        <v>0.007276300000000001</v>
+        <v>7.2763000000000012E-3</v>
       </c>
       <c r="F35">
-        <v>0.0280714</v>
+        <v>2.80714E-2</v>
       </c>
       <c r="G35">
-        <v>0.009469075</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>9.4690750000000004E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -1405,22 +2940,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>0.0004633</v>
+        <v>4.6329999999999999E-4</v>
       </c>
       <c r="D36">
-        <v>0.0016802</v>
+        <v>1.6802E-3</v>
       </c>
       <c r="E36">
-        <v>0.006134500000000001</v>
+        <v>6.1345000000000011E-3</v>
       </c>
       <c r="F36">
-        <v>0.0239816</v>
+        <v>2.3981599999999999E-2</v>
       </c>
       <c r="G36">
-        <v>0.0080649</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>8.0648999999999998E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -1428,22 +2963,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>0.0003911</v>
+        <v>3.9110000000000002E-4</v>
       </c>
       <c r="D37">
-        <v>0.0015293</v>
+        <v>1.5292999999999999E-3</v>
       </c>
       <c r="E37">
-        <v>0.0053754</v>
+        <v>5.3753999999999998E-3</v>
       </c>
       <c r="F37">
-        <v>0.0205785</v>
+        <v>2.05785E-2</v>
       </c>
       <c r="G37">
-        <v>0.006968574999999999</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>6.9685749999999994E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -1451,22 +2986,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>0.0003952999999999999</v>
+        <v>3.952999999999999E-4</v>
       </c>
       <c r="D38">
-        <v>0.001101</v>
+        <v>1.101E-3</v>
       </c>
       <c r="E38">
-        <v>0.0037948</v>
+        <v>3.7948000000000001E-3</v>
       </c>
       <c r="F38">
-        <v>0.0169044</v>
+        <v>1.69044E-2</v>
       </c>
       <c r="G38">
-        <v>0.005548875000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>5.5488750000000009E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -1474,22 +3009,22 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>0.0003601</v>
+        <v>3.6010000000000003E-4</v>
       </c>
       <c r="D39">
-        <v>0.0010562</v>
+        <v>1.0562E-3</v>
       </c>
       <c r="E39">
-        <v>0.0037075</v>
+        <v>3.7074999999999999E-3</v>
       </c>
       <c r="F39">
-        <v>0.0164203</v>
+        <v>1.6420299999999999E-2</v>
       </c>
       <c r="G39">
-        <v>0.005386024999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>5.3860249999999991E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -1497,22 +3032,22 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>0.0003950000000000001</v>
+        <v>3.9500000000000011E-4</v>
       </c>
       <c r="D40">
-        <v>0.0011575</v>
+        <v>1.1574999999999999E-3</v>
       </c>
       <c r="E40">
-        <v>0.003776</v>
+        <v>3.7759999999999998E-3</v>
       </c>
       <c r="F40">
-        <v>0.0141542</v>
+        <v>1.41542E-2</v>
       </c>
       <c r="G40">
-        <v>0.004870675</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>4.8706749999999997E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -1520,22 +3055,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>0.0005711000000000001</v>
+        <v>5.7110000000000006E-4</v>
       </c>
       <c r="D41">
-        <v>0.0018902</v>
+        <v>1.8902000000000001E-3</v>
       </c>
       <c r="E41">
-        <v>0.006659999999999999</v>
+        <v>6.6599999999999993E-3</v>
       </c>
       <c r="F41">
-        <v>0.0253907</v>
+        <v>2.5390699999999999E-2</v>
       </c>
       <c r="G41">
-        <v>0.008628</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>8.6280000000000003E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -1543,22 +3078,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>0.0005524</v>
+        <v>5.5239999999999998E-4</v>
       </c>
       <c r="D42">
-        <v>0.0023361</v>
+        <v>2.3360999999999998E-3</v>
       </c>
       <c r="E42">
-        <v>0.008483200000000002</v>
+        <v>8.4832000000000015E-3</v>
       </c>
       <c r="F42">
-        <v>0.0288907</v>
+        <v>2.8890699999999998E-2</v>
       </c>
       <c r="G42">
-        <v>0.0100656</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>1.0065599999999999E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -1566,22 +3101,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>0.000694</v>
+        <v>6.9399999999999996E-4</v>
       </c>
       <c r="D43">
-        <v>0.0021946</v>
+        <v>2.1946000000000001E-3</v>
       </c>
       <c r="E43">
-        <v>0.007796200000000001</v>
+        <v>7.7962000000000014E-3</v>
       </c>
       <c r="F43">
-        <v>0.0319991</v>
+        <v>3.1999100000000003E-2</v>
       </c>
       <c r="G43">
-        <v>0.010670975</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>1.0670974999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -1589,22 +3124,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>0.0005165</v>
+        <v>5.1650000000000003E-4</v>
       </c>
       <c r="D44">
-        <v>0.0012062</v>
+        <v>1.2061999999999999E-3</v>
       </c>
       <c r="E44">
-        <v>0.0029008</v>
+        <v>2.9007999999999998E-3</v>
       </c>
       <c r="F44">
-        <v>0.008374499999999998</v>
+        <v>8.3744999999999983E-3</v>
       </c>
       <c r="G44">
-        <v>0.0032495</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>3.2494999999999998E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -1612,22 +3147,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>0.0007601</v>
+        <v>7.6009999999999999E-4</v>
       </c>
       <c r="D45">
-        <v>0.0023509</v>
+        <v>2.3509E-3</v>
       </c>
       <c r="E45">
-        <v>0.008473900000000001</v>
+        <v>8.4739000000000012E-3</v>
       </c>
       <c r="F45">
-        <v>0.0361689</v>
+        <v>3.6168899999999997E-2</v>
       </c>
       <c r="G45">
-        <v>0.01193845</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>1.193845E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -1635,22 +3170,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>0.0007051999999999999</v>
+        <v>7.051999999999999E-4</v>
       </c>
       <c r="D46">
-        <v>0.0012229</v>
+        <v>1.2229000000000001E-3</v>
       </c>
       <c r="E46">
-        <v>0.0035711</v>
+        <v>3.5710999999999998E-3</v>
       </c>
       <c r="F46">
-        <v>0.0313029</v>
+        <v>3.1302900000000002E-2</v>
       </c>
       <c r="G46">
-        <v>0.009200525000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>9.2005250000000011E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -1658,22 +3193,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>0.0004032999999999999</v>
+        <v>4.0329999999999988E-4</v>
       </c>
       <c r="D47">
-        <v>0.0015719</v>
+        <v>1.5719E-3</v>
       </c>
       <c r="E47">
-        <v>0.00582</v>
+        <v>5.8199999999999997E-3</v>
       </c>
       <c r="F47">
-        <v>0.024011</v>
+        <v>2.4011000000000001E-2</v>
       </c>
       <c r="G47">
-        <v>0.00795155</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>7.9515499999999999E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -1681,22 +3216,22 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>0.0007434000000000001</v>
+        <v>7.4340000000000007E-4</v>
       </c>
       <c r="D48">
-        <v>0.0015338</v>
+        <v>1.5338000000000001E-3</v>
       </c>
       <c r="E48">
-        <v>0.0063073</v>
+        <v>6.3073000000000001E-3</v>
       </c>
       <c r="F48">
-        <v>0.06186699999999999</v>
+        <v>6.1866999999999991E-2</v>
       </c>
       <c r="G48">
-        <v>0.017612875</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>1.7612875E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -1704,22 +3239,22 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>0.0005126</v>
+        <v>5.1259999999999999E-4</v>
       </c>
       <c r="D49">
-        <v>0.002099600000000001</v>
+        <v>2.0996000000000009E-3</v>
       </c>
       <c r="E49">
-        <v>0.006576900000000001</v>
+        <v>6.576900000000001E-3</v>
       </c>
       <c r="F49">
-        <v>0.0256043</v>
+        <v>2.56043E-2</v>
       </c>
       <c r="G49">
-        <v>0.008698350000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>8.6983500000000005E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1727,22 +3262,22 @@
         <v>55</v>
       </c>
       <c r="C50">
-        <v>0.0004163999999999999</v>
+        <v>4.1639999999999988E-4</v>
       </c>
       <c r="D50">
-        <v>0.0016042</v>
+        <v>1.6042000000000001E-3</v>
       </c>
       <c r="E50">
-        <v>0.005499</v>
+        <v>5.4990000000000004E-3</v>
       </c>
       <c r="F50">
-        <v>0.0207643</v>
+        <v>2.0764299999999999E-2</v>
       </c>
       <c r="G50">
-        <v>0.007070975</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>7.0709750000000002E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -1750,22 +3285,22 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>0.0004467</v>
+        <v>4.4670000000000002E-4</v>
       </c>
       <c r="D51">
-        <v>0.002155</v>
+        <v>2.1549999999999998E-3</v>
       </c>
       <c r="E51">
-        <v>0.0070022</v>
+        <v>7.0022000000000001E-3</v>
       </c>
       <c r="F51">
-        <v>0.0263336</v>
+        <v>2.6333599999999999E-2</v>
       </c>
       <c r="G51">
-        <v>0.008984375000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>8.984375000000001E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -1773,22 +3308,22 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>0.0005104</v>
+        <v>5.1040000000000005E-4</v>
       </c>
       <c r="D52">
-        <v>0.0021238</v>
+        <v>2.1237999999999999E-3</v>
       </c>
       <c r="E52">
-        <v>0.0073606</v>
+        <v>7.3606000000000001E-3</v>
       </c>
       <c r="F52">
-        <v>0.0283252</v>
+        <v>2.8325199999999998E-2</v>
       </c>
       <c r="G52">
-        <v>0.00958</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>9.58E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -1796,22 +3331,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>0.0004326</v>
+        <v>4.326E-4</v>
       </c>
       <c r="D53">
-        <v>0.0016059</v>
+        <v>1.6058999999999999E-3</v>
       </c>
       <c r="E53">
-        <v>0.0053676</v>
+        <v>5.3676000000000001E-3</v>
       </c>
       <c r="F53">
-        <v>0.020551</v>
+        <v>2.0551E-2</v>
       </c>
       <c r="G53">
-        <v>0.006989275</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>6.9892749999999997E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -1819,22 +3354,22 @@
         <v>59</v>
       </c>
       <c r="C54">
-        <v>0.0003967999999999999</v>
+        <v>3.9679999999999989E-4</v>
       </c>
       <c r="D54">
-        <v>0.0015303</v>
+        <v>1.5303000000000001E-3</v>
       </c>
       <c r="E54">
-        <v>0.005432000000000001</v>
+        <v>5.4320000000000011E-3</v>
       </c>
       <c r="F54">
-        <v>0.0209878</v>
+        <v>2.0987800000000001E-2</v>
       </c>
       <c r="G54">
-        <v>0.007086725</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>7.0867250000000003E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -1842,22 +3377,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>0.0004108000000000001</v>
+        <v>4.1080000000000012E-4</v>
       </c>
       <c r="D55">
-        <v>0.001104</v>
+        <v>1.1039999999999999E-3</v>
       </c>
       <c r="E55">
-        <v>0.0038278</v>
+        <v>3.8278000000000001E-3</v>
       </c>
       <c r="F55">
-        <v>0.0165787</v>
+        <v>1.6578699999999998E-2</v>
       </c>
       <c r="G55">
-        <v>0.005480324999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>5.4803249999999994E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -1865,22 +3400,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>0.0004284</v>
+        <v>4.284E-4</v>
       </c>
       <c r="D56">
-        <v>0.0012153</v>
+        <v>1.2153000000000001E-3</v>
       </c>
       <c r="E56">
-        <v>0.0038754</v>
+        <v>3.8754000000000002E-3</v>
       </c>
       <c r="F56">
-        <v>0.0142977</v>
+        <v>1.42977E-2</v>
       </c>
       <c r="G56">
-        <v>0.004954200000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>4.9542000000000006E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1888,22 +3423,22 @@
         <v>62</v>
       </c>
       <c r="C57">
-        <v>0.0003999</v>
+        <v>3.9990000000000002E-4</v>
       </c>
       <c r="D57">
-        <v>0.0011734</v>
+        <v>1.1734E-3</v>
       </c>
       <c r="E57">
-        <v>0.0038138</v>
+        <v>3.8138E-3</v>
       </c>
       <c r="F57">
-        <v>0.0141501</v>
+        <v>1.4150100000000001E-2</v>
       </c>
       <c r="G57">
-        <v>0.004884299999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>4.8842999999999994E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -1911,22 +3446,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>0.0005735999999999998</v>
+        <v>5.7359999999999985E-4</v>
       </c>
       <c r="D58">
-        <v>0.0023144</v>
+        <v>2.3143999999999999E-3</v>
       </c>
       <c r="E58">
-        <v>0.008562900000000002</v>
+        <v>8.5629000000000018E-3</v>
       </c>
       <c r="F58">
-        <v>0.0290803</v>
+        <v>2.90803E-2</v>
       </c>
       <c r="G58">
-        <v>0.0101328</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>1.0132800000000001E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -1934,22 +3469,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>0.0007586</v>
+        <v>7.5860000000000001E-4</v>
       </c>
       <c r="D59">
-        <v>0.0013194</v>
+        <v>1.3194000000000001E-3</v>
       </c>
       <c r="E59">
-        <v>0.003854899999999999</v>
+        <v>3.8548999999999992E-3</v>
       </c>
       <c r="F59">
-        <v>0.0326241</v>
+        <v>3.2624100000000003E-2</v>
       </c>
       <c r="G59">
-        <v>0.00963925</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>9.6392500000000002E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -1957,22 +3492,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>0.0004424</v>
+        <v>4.4240000000000002E-4</v>
       </c>
       <c r="D60">
-        <v>0.0016312</v>
+        <v>1.6312E-3</v>
       </c>
       <c r="E60">
-        <v>0.005613599999999999</v>
+        <v>5.613599999999999E-3</v>
       </c>
       <c r="F60">
-        <v>0.0210032</v>
+        <v>2.10032E-2</v>
       </c>
       <c r="G60">
-        <v>0.007172599999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>7.1725999999999986E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -1980,22 +3515,22 @@
         <v>66</v>
       </c>
       <c r="C61">
-        <v>0.0004982</v>
+        <v>4.9819999999999997E-4</v>
       </c>
       <c r="D61">
-        <v>0.0022641</v>
+        <v>2.2640999999999998E-3</v>
       </c>
       <c r="E61">
-        <v>0.0071022</v>
+        <v>7.1022000000000004E-3</v>
       </c>
       <c r="F61">
-        <v>0.0264714</v>
+        <v>2.6471399999999999E-2</v>
       </c>
       <c r="G61">
-        <v>0.009083974999999999</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
+        <v>9.0839749999999993E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -2003,22 +3538,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>0.0003871</v>
+        <v>3.8709999999999998E-4</v>
       </c>
       <c r="D62">
-        <v>0.0017042</v>
+        <v>1.7041999999999999E-3</v>
       </c>
       <c r="E62">
-        <v>0.0059132</v>
+        <v>5.9132000000000004E-3</v>
       </c>
       <c r="F62">
-        <v>0.022611</v>
+        <v>2.2610999999999999E-2</v>
       </c>
       <c r="G62">
-        <v>0.007653874999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>7.6538749999999992E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -2026,22 +3561,22 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>0.0004715</v>
+        <v>4.7150000000000002E-4</v>
       </c>
       <c r="D63">
-        <v>0.0016366</v>
+        <v>1.6366E-3</v>
       </c>
       <c r="E63">
-        <v>0.0054604</v>
+        <v>5.4603999999999998E-3</v>
       </c>
       <c r="F63">
-        <v>0.0207664</v>
+        <v>2.0766400000000001E-2</v>
       </c>
       <c r="G63">
-        <v>0.007083725000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>7.0837250000000008E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -2049,22 +3584,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>0.0004404</v>
+        <v>4.4040000000000003E-4</v>
       </c>
       <c r="D64">
-        <v>0.001227</v>
+        <v>1.227E-3</v>
       </c>
       <c r="E64">
-        <v>0.0038623</v>
+        <v>3.8622999999999999E-3</v>
       </c>
       <c r="F64">
-        <v>0.0145051</v>
+        <v>1.45051E-2</v>
       </c>
       <c r="G64">
-        <v>0.0050087</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>5.0086999999999996E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -2072,32 +3607,33 @@
         <v>70</v>
       </c>
       <c r="C65">
-        <v>0.0004175</v>
+        <v>4.1750000000000001E-4</v>
       </c>
       <c r="D65">
-        <v>0.001875</v>
+        <v>1.8749999999999999E-3</v>
       </c>
       <c r="E65">
-        <v>0.0060134</v>
+        <v>6.0134000000000003E-3</v>
       </c>
       <c r="F65">
-        <v>0.0236586</v>
+        <v>2.3658599999999998E-2</v>
       </c>
       <c r="G65">
-        <v>0.007991125</v>
+        <v>7.991125E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2120,7 +3656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2143,7 +3679,7 @@
         <v>71.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2166,7 +3702,7 @@
         <v>71.25</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -2189,7 +3725,7 @@
         <v>86.75</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -2212,7 +3748,7 @@
         <v>71.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -2235,7 +3771,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -2258,7 +3794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -2281,7 +3817,7 @@
         <v>71.25</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -2304,7 +3840,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2327,7 +3863,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2350,7 +3886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2373,7 +3909,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -2396,7 +3932,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -2419,7 +3955,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -2442,7 +3978,7 @@
         <v>85.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -2465,7 +4001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -2488,7 +4024,7 @@
         <v>71.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -2511,7 +4047,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -2534,7 +4070,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -2557,7 +4093,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -2580,7 +4116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2603,7 +4139,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -2626,7 +4162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -2649,7 +4185,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -2672,7 +4208,7 @@
         <v>75.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -2695,7 +4231,7 @@
         <v>85.75</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -2718,7 +4254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -2741,7 +4277,7 @@
         <v>78.75</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -2764,7 +4300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -2787,7 +4323,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -2810,7 +4346,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2833,7 +4369,7 @@
         <v>82.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -2856,7 +4392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -2879,7 +4415,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -2902,7 +4438,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -2925,7 +4461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -2948,7 +4484,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -2971,7 +4507,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -2994,7 +4530,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -3017,7 +4553,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -3040,7 +4576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -3063,7 +4599,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -3086,7 +4622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -3109,7 +4645,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -3132,7 +4668,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -3155,7 +4691,7 @@
         <v>81.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -3178,7 +4714,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -3201,7 +4737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -3224,7 +4760,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -3247,7 +4783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -3270,7 +4806,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -3293,7 +4829,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -3316,7 +4852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -3339,7 +4875,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -3362,7 +4898,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -3385,7 +4921,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -3408,7 +4944,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -3431,7 +4967,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -3454,7 +4990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -3477,7 +5013,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -3500,7 +5036,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -3523,7 +5059,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -3546,7 +5082,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -3569,7 +5105,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -3598,11 +5134,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3625,7 +5161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -3633,22 +5169,22 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D2">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E2">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F2">
         <v>193.6639969244288</v>
       </c>
       <c r="G2">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3656,22 +5192,22 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D3">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E3">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F3">
         <v>193.6639969244288</v>
       </c>
       <c r="G3">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3685,16 +5221,16 @@
         <v>50.87005768508881</v>
       </c>
       <c r="E4">
-        <v>106.0832611206852</v>
+        <v>106.08326112068519</v>
       </c>
       <c r="F4">
-        <v>215.9238815542512</v>
+        <v>215.92388155425121</v>
       </c>
       <c r="G4">
-        <v>99.10838738653231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>99.108387386532314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -3702,22 +5238,22 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D5">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E5">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F5">
         <v>193.6639969244288</v>
       </c>
       <c r="G5">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -3725,22 +5261,22 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D6">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E6">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F6">
         <v>193.6639969244288</v>
       </c>
       <c r="G6">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -3748,22 +5284,22 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D7">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E7">
-        <v>93.2032658581451</v>
+        <v>93.203265858145102</v>
       </c>
       <c r="F7">
-        <v>187.5929117988749</v>
+        <v>187.59291179887489</v>
       </c>
       <c r="G7">
-        <v>87.33691238960859</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>87.336912389608585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -3771,22 +5307,22 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D8">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E8">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F8">
         <v>193.6639969244288</v>
       </c>
       <c r="G8">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -3797,19 +5333,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D9">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E9">
-        <v>99.63961030678929</v>
+        <v>99.639610306789294</v>
       </c>
       <c r="F9">
-        <v>201.8650070512055</v>
+        <v>201.86500705120551</v>
       </c>
       <c r="G9">
-        <v>93.39696961967</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>93.396969619670003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -3817,10 +5353,10 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>24.14213562373095</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D10">
-        <v>49.698484809835</v>
+        <v>49.698484809835001</v>
       </c>
       <c r="E10">
         <v>100.8111831820431</v>
@@ -3829,10 +5365,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G10">
-        <v>94.42209588551708</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>94.422095885517081</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -3840,22 +5376,22 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D11">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E11">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F11">
-        <v>189.6538348592767</v>
+        <v>189.65383485927671</v>
       </c>
       <c r="G11">
-        <v>87.83084116930945</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>87.830841169309451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -3863,22 +5399,22 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D12">
-        <v>47.94112549695429</v>
+        <v>47.941125496954292</v>
       </c>
       <c r="E12">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F12">
         <v>193.6639969244288</v>
       </c>
       <c r="G12">
-        <v>90.17514421272202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>90.175144212722017</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -3886,22 +5422,22 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>22.63292806537241</v>
+        <v>22.632928065372411</v>
       </c>
       <c r="D13">
-        <v>47.81214177348095</v>
+        <v>47.812141773480953</v>
       </c>
       <c r="E13">
-        <v>96.76314452072573</v>
+        <v>96.763144520725731</v>
       </c>
       <c r="F13">
-        <v>193.9828973923969</v>
+        <v>193.98289739239689</v>
       </c>
       <c r="G13">
-        <v>90.29777793799398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>90.297777937993985</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -3909,10 +5445,10 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>24.72792206135785</v>
+        <v>24.727922061357852</v>
       </c>
       <c r="D14">
-        <v>52.04163056034262</v>
+        <v>52.041630560342618</v>
       </c>
       <c r="E14">
         <v>105.4974746830583</v>
@@ -3921,10 +5457,10 @@
         <v>212.9949493661166</v>
       </c>
       <c r="G14">
-        <v>98.81549416771885</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>98.815494167718853</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -3932,7 +5468,7 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>24.97056274847714</v>
+        <v>24.970562748477139</v>
       </c>
       <c r="D15">
         <v>52.87005768508881</v>
@@ -3941,13 +5477,13 @@
         <v>107.1543289325507</v>
       </c>
       <c r="F15">
-        <v>215.7228714274746</v>
+        <v>215.72287142747459</v>
       </c>
       <c r="G15">
         <v>100.1794551983978</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -3955,22 +5491,22 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D16">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E16">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F16">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G16">
-        <v>87.25337971078574</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>87.253379710785737</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -3978,22 +5514,22 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D17">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E17">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F17">
         <v>193.6639969244288</v>
       </c>
       <c r="G17">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4001,22 +5537,22 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D18">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E18">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F18">
         <v>193.6639969244288</v>
       </c>
       <c r="G18">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4027,7 +5563,7 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D19">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E19">
         <v>100.8111831820431</v>
@@ -4036,10 +5572,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G19">
-        <v>94.27564927611036</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>94.275649276110357</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4047,22 +5583,22 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D20">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E20">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F20">
         <v>193.6639969244288</v>
       </c>
       <c r="G20">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4070,22 +5606,22 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D21">
-        <v>47.01219330881975</v>
+        <v>47.012193308819747</v>
       </c>
       <c r="E21">
-        <v>95.17930953468691</v>
+        <v>95.179309534686908</v>
       </c>
       <c r="F21">
-        <v>191.5449991519585</v>
+        <v>191.54499915195851</v>
       </c>
       <c r="G21">
-        <v>89.17676618598557</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>89.176766185985571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4093,22 +5629,22 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D22">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E22">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F22">
         <v>193.6639969244288</v>
       </c>
       <c r="G22">
-        <v>90.02869760331529</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>90.028697603315294</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -4116,22 +5652,22 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D23">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E23">
-        <v>93.29870679092078</v>
+        <v>93.298706790920775</v>
       </c>
       <c r="F23">
-        <v>187.6855785610423</v>
+        <v>187.68557856104229</v>
       </c>
       <c r="G23">
-        <v>87.38393931334436</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>87.383939313344356</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -4139,22 +5675,22 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>22.63292806537241</v>
+        <v>22.632928065372411</v>
       </c>
       <c r="D24">
-        <v>46.34657557770468</v>
+        <v>46.346575577704677</v>
       </c>
       <c r="E24">
-        <v>93.83845879691515</v>
+        <v>93.838458796915148</v>
       </c>
       <c r="F24">
         <v>188.8474884458995</v>
       </c>
       <c r="G24">
-        <v>87.91636272147292</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>87.916362721472922</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -4165,19 +5701,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D25">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E25">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F25">
         <v>198.9360748630709</v>
       </c>
       <c r="G25">
-        <v>92.3718433538229</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>92.371843353822896</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -4185,7 +5721,7 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24.97056274847714</v>
+        <v>24.970562748477139</v>
       </c>
       <c r="D26">
         <v>52.87005768508881</v>
@@ -4194,13 +5730,13 @@
         <v>106.3259018078045</v>
       </c>
       <c r="F26">
-        <v>213.2375900532359</v>
+        <v>213.23759005323589</v>
       </c>
       <c r="G26">
-        <v>99.35102807365161</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>99.351028073651605</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -4208,22 +5744,22 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>22.9781948590917</v>
+        <v>22.978194859091701</v>
       </c>
       <c r="D27">
-        <v>46.80296455015541</v>
+        <v>46.802964550155409</v>
       </c>
       <c r="E27">
-        <v>94.58282965890581</v>
+        <v>94.582829658905808</v>
       </c>
       <c r="F27">
-        <v>192.5016247825731</v>
+        <v>192.50162478257309</v>
       </c>
       <c r="G27">
-        <v>89.2164034626815</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>89.216403462681498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -4231,10 +5767,10 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>24.14213562373095</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D28">
-        <v>49.698484809835</v>
+        <v>49.698484809835001</v>
       </c>
       <c r="E28">
         <v>100.8111831820431</v>
@@ -4243,10 +5779,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G28">
-        <v>94.42209588551708</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>94.422095885517081</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -4254,22 +5790,22 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D29">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E29">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F29">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G29">
-        <v>87.25337971078574</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>87.253379710785737</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -4277,22 +5813,22 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>23.77654923889891</v>
+        <v>23.776549238898909</v>
       </c>
       <c r="D30">
-        <v>47.81214177348095</v>
+        <v>47.812141773480953</v>
       </c>
       <c r="E30">
-        <v>96.76314452072573</v>
+        <v>96.763144520725731</v>
       </c>
       <c r="F30">
-        <v>193.9828973923969</v>
+        <v>193.98289739239689</v>
       </c>
       <c r="G30">
-        <v>90.58368323137562</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>90.583683231375616</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -4303,19 +5839,19 @@
         <v>24.24988430144958</v>
       </c>
       <c r="D31">
-        <v>48.96640874749266</v>
+        <v>48.966408747492657</v>
       </c>
       <c r="E31">
-        <v>98.86836387794982</v>
+        <v>98.868363877949818</v>
       </c>
       <c r="F31">
         <v>198.709949036832</v>
       </c>
       <c r="G31">
-        <v>92.69865149093101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>92.698651490931013</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -4323,22 +5859,22 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>24.97056274847714</v>
+        <v>24.970562748477139</v>
       </c>
       <c r="D32">
-        <v>49.1126983722081</v>
+        <v>49.112698372208101</v>
       </c>
       <c r="E32">
         <v>101.39696961967</v>
       </c>
       <c r="F32">
-        <v>212.4091629284898</v>
+        <v>212.40916292848979</v>
       </c>
       <c r="G32">
-        <v>96.97234841721126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>96.972348417211265</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -4346,22 +5882,22 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D33">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E33">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F33">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G33">
-        <v>87.25337971078574</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>87.253379710785737</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4369,10 +5905,10 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D34">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E34">
         <v>100.8111831820431</v>
@@ -4381,10 +5917,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G34">
-        <v>94.71498910433053</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>94.714989104330527</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -4392,10 +5928,10 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>24.14213562373095</v>
+        <v>24.142135623730951</v>
       </c>
       <c r="D35">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E35">
         <v>100.8111831820431</v>
@@ -4404,10 +5940,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G35">
-        <v>94.42209588551708</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>94.422095885517081</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4415,22 +5951,22 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D36">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E36">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F36">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G36">
-        <v>87.25337971078574</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>87.253379710785737</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -4438,22 +5974,22 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D37">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E37">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F37">
         <v>193.6639969244288</v>
       </c>
       <c r="G37">
-        <v>90.61448404094219</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>90.614484040942187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -4461,22 +5997,22 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>22.94812211415272</v>
+        <v>22.948122114152721</v>
       </c>
       <c r="D38">
-        <v>48.13413213893392</v>
+        <v>48.134132138933921</v>
       </c>
       <c r="E38">
-        <v>97.5896634233869</v>
+        <v>97.589663423386895</v>
       </c>
       <c r="F38">
         <v>196.5117868477252</v>
       </c>
       <c r="G38">
-        <v>91.29592613104968</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>91.295926131049683</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -4487,7 +6023,7 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D39">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E39">
         <v>100.8111831820431</v>
@@ -4496,10 +6032,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G39">
-        <v>94.27564927611036</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>94.275649276110357</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -4510,7 +6046,7 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D40">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E40">
         <v>100.8111831820431</v>
@@ -4519,10 +6055,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G40">
-        <v>94.27564927611036</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>94.275649276110357</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -4530,22 +6066,22 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D41">
-        <v>47.01219330881975</v>
+        <v>47.012193308819747</v>
       </c>
       <c r="E41">
-        <v>95.17930953468691</v>
+        <v>95.179309534686908</v>
       </c>
       <c r="F41">
-        <v>191.5449991519585</v>
+        <v>191.54499915195851</v>
       </c>
       <c r="G41">
-        <v>89.17676618598557</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>89.176766185985571</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -4553,22 +6089,22 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D42">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E42">
-        <v>98.46803743153546</v>
+        <v>98.468037431535464</v>
       </c>
       <c r="F42">
         <v>203.0365799264593</v>
       </c>
       <c r="G42">
-        <v>92.95762979144982</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>92.957629791449818</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -4576,22 +6112,22 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D43">
-        <v>47.01219330881975</v>
+        <v>47.012193308819747</v>
       </c>
       <c r="E43">
-        <v>95.17930953468691</v>
+        <v>95.179309534686908</v>
       </c>
       <c r="F43">
-        <v>191.5449991519585</v>
+        <v>191.54499915195851</v>
       </c>
       <c r="G43">
-        <v>89.17676618598557</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>89.176766185985571</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -4599,22 +6135,22 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>22.63292806537241</v>
+        <v>22.632928065372411</v>
       </c>
       <c r="D44">
-        <v>46.34657557770468</v>
+        <v>46.346575577704677</v>
       </c>
       <c r="E44">
-        <v>93.83845879691515</v>
+        <v>93.838458796915148</v>
       </c>
       <c r="F44">
         <v>188.8474884458995</v>
       </c>
       <c r="G44">
-        <v>87.91636272147292</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>87.916362721472922</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -4622,22 +6158,22 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>23.80662198383789</v>
+        <v>23.806621983837889</v>
       </c>
       <c r="D45">
-        <v>48.83569181888343</v>
+        <v>48.835691818883433</v>
       </c>
       <c r="E45">
-        <v>98.86836387794982</v>
+        <v>98.868363877949818</v>
       </c>
       <c r="F45">
         <v>198.709949036832</v>
       </c>
       <c r="G45">
-        <v>92.55515667937578</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>92.555156679375784</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -4645,22 +6181,22 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>24.97056274847714</v>
+        <v>24.970562748477139</v>
       </c>
       <c r="D46">
-        <v>48.52691193458118</v>
+        <v>48.526911934581179</v>
       </c>
       <c r="E46">
-        <v>99.63961030678929</v>
+        <v>99.639610306789294</v>
       </c>
       <c r="F46">
-        <v>213.2375900532359</v>
+        <v>213.23759005323589</v>
       </c>
       <c r="G46">
-        <v>96.5936687607709</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>96.593668760770896</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -4668,22 +6204,22 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>22.9781948590917</v>
+        <v>22.978194859091701</v>
       </c>
       <c r="D47">
-        <v>46.80296455015541</v>
+        <v>46.802964550155409</v>
       </c>
       <c r="E47">
-        <v>94.58282965890581</v>
+        <v>94.582829658905808</v>
       </c>
       <c r="F47">
-        <v>192.5016247825731</v>
+        <v>192.50162478257309</v>
       </c>
       <c r="G47">
-        <v>89.2164034626815</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>89.216403462681498</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -4694,19 +6230,19 @@
         <v>24.24988430144958</v>
       </c>
       <c r="D48">
-        <v>46.65728395407391</v>
+        <v>46.657283954073911</v>
       </c>
       <c r="E48">
-        <v>94.28838602210131</v>
+        <v>94.288386022101307</v>
       </c>
       <c r="F48">
-        <v>200.5402957337251</v>
+        <v>200.54029573372509</v>
       </c>
       <c r="G48">
-        <v>91.43396250283749</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>91.433962502837488</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -4717,19 +6253,19 @@
         <v>24.26221910942175</v>
       </c>
       <c r="D49">
-        <v>47.71474284512288</v>
+        <v>47.714742845122878</v>
       </c>
       <c r="E49">
-        <v>96.35556830690527</v>
+        <v>96.355568306905269</v>
       </c>
       <c r="F49">
-        <v>193.6796396249865</v>
+        <v>193.67963962498649</v>
       </c>
       <c r="G49">
-        <v>90.50304247160911</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>90.503042471609106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -4740,19 +6276,19 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D50">
-        <v>47.35533905932738</v>
+        <v>47.355339059327378</v>
       </c>
       <c r="E50">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F50">
         <v>193.6639969244288</v>
       </c>
       <c r="G50">
-        <v>90.17514421272202</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>90.175144212722017</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -4760,10 +6296,10 @@
         <v>56</v>
       </c>
       <c r="C51">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D51">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E51">
         <v>100.8111831820431</v>
@@ -4772,10 +6308,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G51">
-        <v>94.71498910433053</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>94.714989104330527</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -4783,22 +6319,22 @@
         <v>57</v>
       </c>
       <c r="C52">
-        <v>22.9781948590917</v>
+        <v>22.978194859091701</v>
       </c>
       <c r="D52">
-        <v>47.71474284512288</v>
+        <v>47.714742845122878</v>
       </c>
       <c r="E52">
-        <v>95.52841180524675</v>
+        <v>95.528411805246748</v>
       </c>
       <c r="F52">
         <v>192.3107767209485</v>
       </c>
       <c r="G52">
-        <v>89.63303155760246</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>89.633031557602465</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -4806,22 +6342,22 @@
         <v>58</v>
       </c>
       <c r="C53">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D53">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E53">
-        <v>96.12489168102785</v>
+        <v>96.124891681027847</v>
       </c>
       <c r="F53">
         <v>193.6639969244288</v>
       </c>
       <c r="G53">
-        <v>90.61448404094219</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>90.614484040942187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -4832,19 +6368,19 @@
         <v>24.99851445020445</v>
       </c>
       <c r="D54">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E54">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F54">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G54">
-        <v>87.87118321562048</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>87.871183215620476</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -4852,22 +6388,22 @@
         <v>60</v>
       </c>
       <c r="C55">
-        <v>22.94812211415272</v>
+        <v>22.948122114152721</v>
       </c>
       <c r="D55">
-        <v>48.13413213893392</v>
+        <v>48.134132138933921</v>
       </c>
       <c r="E55">
-        <v>97.5896634233869</v>
+        <v>97.589663423386895</v>
       </c>
       <c r="F55">
         <v>196.5117868477252</v>
       </c>
       <c r="G55">
-        <v>91.29592613104968</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>91.295926131049683</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -4875,22 +6411,22 @@
         <v>61</v>
       </c>
       <c r="C56">
-        <v>22.94812211415272</v>
+        <v>22.948122114152721</v>
       </c>
       <c r="D56">
-        <v>48.13413213893392</v>
+        <v>48.134132138933921</v>
       </c>
       <c r="E56">
-        <v>97.5896634233869</v>
+        <v>97.589663423386895</v>
       </c>
       <c r="F56">
         <v>196.5117868477252</v>
       </c>
       <c r="G56">
-        <v>91.29592613104968</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>91.295926131049683</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -4901,7 +6437,7 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D57">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E57">
         <v>100.8111831820431</v>
@@ -4910,10 +6446,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G57">
-        <v>94.27564927611036</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>94.275649276110357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -4921,22 +6457,22 @@
         <v>63</v>
       </c>
       <c r="C58">
-        <v>22.97056274847714</v>
+        <v>22.970562748477139</v>
       </c>
       <c r="D58">
-        <v>47.01219330881975</v>
+        <v>47.012193308819747</v>
       </c>
       <c r="E58">
-        <v>95.6963231731842</v>
+        <v>95.696323173184197</v>
       </c>
       <c r="F58">
         <v>196.5117868477252</v>
       </c>
       <c r="G58">
-        <v>90.54771651955157</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>90.547716519551571</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -4944,22 +6480,22 @@
         <v>64</v>
       </c>
       <c r="C59">
-        <v>23.80662198383789</v>
+        <v>23.806621983837889</v>
       </c>
       <c r="D59">
-        <v>46.34657557770468</v>
+        <v>46.346575577704677</v>
       </c>
       <c r="E59">
-        <v>93.83845879691515</v>
+        <v>93.838458796915148</v>
       </c>
       <c r="F59">
-        <v>200.5402957337251</v>
+        <v>200.54029573372509</v>
       </c>
       <c r="G59">
-        <v>91.1329880230457</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
+        <v>91.132988023045698</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -4967,22 +6503,22 @@
         <v>65</v>
       </c>
       <c r="C60">
-        <v>22.63292806537241</v>
+        <v>22.632928065372411</v>
       </c>
       <c r="D60">
-        <v>46.02417147054884</v>
+        <v>46.024171470548843</v>
       </c>
       <c r="E60">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F60">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G60">
-        <v>87.27978661941248</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
+        <v>87.279786619412477</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -4993,10 +6529,10 @@
         <v>23.9102632953472</v>
       </c>
       <c r="D61">
-        <v>47.71474284512288</v>
+        <v>47.714742845122878</v>
       </c>
       <c r="E61">
-        <v>95.52841180524675</v>
+        <v>95.528411805246748</v>
       </c>
       <c r="F61">
         <v>192.3107767209485</v>
@@ -5005,7 +6541,7 @@
         <v>89.86604866666633</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -5013,22 +6549,22 @@
         <v>67</v>
       </c>
       <c r="C62">
-        <v>25.31370849898476</v>
+        <v>25.313708498984759</v>
       </c>
       <c r="D62">
-        <v>49.69848480983499</v>
+        <v>49.698484809834987</v>
       </c>
       <c r="E62">
-        <v>113.3553390593274</v>
+        <v>113.35533905932741</v>
       </c>
       <c r="F62">
-        <v>227.2964645562816</v>
+        <v>227.29646455628159</v>
       </c>
       <c r="G62">
-        <v>103.9159992311072</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
+        <v>103.91599923110719</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -5036,22 +6572,22 @@
         <v>68</v>
       </c>
       <c r="C63">
-        <v>22.52730043086546</v>
+        <v>22.527300430865459</v>
       </c>
       <c r="D63">
-        <v>47.71474284512288</v>
+        <v>47.714742845122878</v>
       </c>
       <c r="E63">
-        <v>93.1180579165468</v>
+        <v>93.118057916546803</v>
       </c>
       <c r="F63">
-        <v>187.3439890251819</v>
+        <v>187.34398902518191</v>
       </c>
       <c r="G63">
-        <v>87.67602255442925</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+        <v>87.676022554429252</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -5059,22 +6595,22 @@
         <v>69</v>
       </c>
       <c r="C64">
-        <v>22.94812211415272</v>
+        <v>22.948122114152721</v>
       </c>
       <c r="D64">
-        <v>48.13413213893392</v>
+        <v>48.134132138933921</v>
       </c>
       <c r="E64">
-        <v>97.5896634233869</v>
+        <v>97.589663423386895</v>
       </c>
       <c r="F64">
         <v>196.5117868477252</v>
       </c>
       <c r="G64">
-        <v>91.29592613104968</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+        <v>91.295926131049683</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -5085,7 +6621,7 @@
         <v>23.9102632953472</v>
       </c>
       <c r="D65">
-        <v>47.71474284512288</v>
+        <v>47.714742845122878</v>
       </c>
       <c r="E65">
         <v>110.3485052948463</v>
@@ -5103,11 +6639,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5130,7 +6666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -5153,7 +6689,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5176,7 +6712,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5199,7 +6735,7 @@
         <v>203.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -5222,7 +6758,7 @@
         <v>369.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -5245,7 +6781,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -5268,7 +6804,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -5291,7 +6827,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -5314,7 +6850,7 @@
         <v>228.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -5337,7 +6873,7 @@
         <v>315.25</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -5360,7 +6896,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -5383,7 +6919,7 @@
         <v>354.25</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -5406,7 +6942,7 @@
         <v>203.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -5429,7 +6965,7 @@
         <v>202.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -5452,7 +6988,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -5475,7 +7011,7 @@
         <v>369.25</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -5498,7 +7034,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -5521,7 +7057,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -5544,7 +7080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -5567,7 +7103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -5590,7 +7126,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -5613,7 +7149,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -5636,7 +7172,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -5659,7 +7195,7 @@
         <v>228.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -5682,7 +7218,7 @@
         <v>216.75</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -5705,7 +7241,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -5728,7 +7264,7 @@
         <v>315.25</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -5751,7 +7287,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -5774,7 +7310,7 @@
         <v>354.25</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -5797,7 +7333,7 @@
         <v>202.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -5820,7 +7356,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -5843,7 +7379,7 @@
         <v>251.25</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -5866,7 +7402,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -5889,7 +7425,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -5912,7 +7448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -5935,7 +7471,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -5958,7 +7494,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -5981,7 +7517,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -6004,7 +7540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -6027,7 +7563,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -6050,7 +7586,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -6073,7 +7609,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -6096,7 +7632,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -6119,7 +7655,7 @@
         <v>216.75</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -6142,7 +7678,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -6165,7 +7701,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -6188,7 +7724,7 @@
         <v>301.25</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -6211,7 +7747,7 @@
         <v>251.25</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -6234,7 +7770,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -6257,7 +7793,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -6280,7 +7816,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -6303,7 +7839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -6326,7 +7862,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -6349,7 +7885,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -6372,7 +7908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -6395,7 +7931,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -6418,7 +7954,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -6441,7 +7977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -6464,7 +8000,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -6487,7 +8023,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -6510,7 +8046,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -6533,7 +8069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -6556,7 +8092,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -6579,7 +8115,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -6608,11 +8144,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6635,7 +8171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -6658,7 +8194,7 @@
         <v>1619.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -6681,7 +8217,7 @@
         <v>835.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -6704,7 +8240,7 @@
         <v>146.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -6727,7 +8263,7 @@
         <v>942.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -6750,7 +8286,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -6773,7 +8309,7 @@
         <v>1619.75</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -6796,7 +8332,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -6819,7 +8355,7 @@
         <v>122.75</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -6842,7 +8378,7 @@
         <v>782.75</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -6865,7 +8401,7 @@
         <v>835.75</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -6888,7 +8424,7 @@
         <v>821.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -6911,7 +8447,7 @@
         <v>146.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -6934,7 +8470,7 @@
         <v>142.75</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -6957,7 +8493,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -6980,7 +8516,7 @@
         <v>942.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -7003,7 +8539,7 @@
         <v>936.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -7026,7 +8562,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -7049,7 +8585,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -7072,7 +8608,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -7095,7 +8631,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -7118,7 +8654,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -7141,7 +8677,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -7164,7 +8700,7 @@
         <v>122.75</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -7187,7 +8723,7 @@
         <v>112.25</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -7210,7 +8746,7 @@
         <v>414.5</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -7233,7 +8769,7 @@
         <v>782.75</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -7256,7 +8792,7 @@
         <v>804.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -7279,7 +8815,7 @@
         <v>821.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -7302,7 +8838,7 @@
         <v>142.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -7325,7 +8861,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -7348,7 +8884,7 @@
         <v>266.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -7371,7 +8907,7 @@
         <v>936.25</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -7394,7 +8930,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -7417,7 +8953,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -7440,7 +8976,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -7463,7 +8999,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -7486,7 +9022,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -7509,7 +9045,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -7532,7 +9068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -7555,7 +9091,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -7578,7 +9114,7 @@
         <v>28.75</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -7601,7 +9137,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -7624,7 +9160,7 @@
         <v>112.25</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -7647,7 +9183,7 @@
         <v>414.5</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -7670,7 +9206,7 @@
         <v>337.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -7693,7 +9229,7 @@
         <v>804.5</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -7716,7 +9252,7 @@
         <v>266.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -7739,7 +9275,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -7762,7 +9298,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -7785,7 +9321,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -7808,7 +9344,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -7831,7 +9367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -7854,7 +9390,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -7877,7 +9413,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -7900,7 +9436,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -7923,7 +9459,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -7946,7 +9482,7 @@
         <v>28.75</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -7969,7 +9505,7 @@
         <v>337.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -7992,7 +9528,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -8015,7 +9551,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -8038,7 +9574,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -8061,7 +9597,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -8084,7 +9620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>
@@ -8113,11 +9649,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8140,7 +9676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -8163,7 +9699,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -8186,7 +9722,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -8209,7 +9745,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -8232,7 +9768,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
@@ -8255,7 +9791,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1</v>
       </c>
@@ -8278,7 +9814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -8301,7 +9837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -8324,7 +9860,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -8347,7 +9883,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -8370,7 +9906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -8393,7 +9929,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -8416,7 +9952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -8439,7 +9975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -8462,7 +9998,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -8485,7 +10021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -8508,7 +10044,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -8531,7 +10067,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -8554,7 +10090,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -8577,7 +10113,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -8600,7 +10136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -8623,7 +10159,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -8646,7 +10182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>3</v>
       </c>
@@ -8669,7 +10205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>3</v>
       </c>
@@ -8692,7 +10228,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>3</v>
       </c>
@@ -8715,7 +10251,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>3</v>
       </c>
@@ -8738,7 +10274,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -8761,7 +10297,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -8784,7 +10320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -8807,7 +10343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -8830,7 +10366,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -8853,7 +10389,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -8876,7 +10412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -8899,7 +10435,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -8922,7 +10458,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -8945,7 +10481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -8968,7 +10504,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -8991,7 +10527,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -9014,7 +10550,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>3</v>
       </c>
@@ -9037,7 +10573,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>3</v>
       </c>
@@ -9060,7 +10596,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>3</v>
       </c>
@@ -9083,7 +10619,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>3</v>
       </c>
@@ -9106,7 +10642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>4</v>
       </c>
@@ -9129,7 +10665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>4</v>
       </c>
@@ -9152,7 +10688,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>4</v>
       </c>
@@ -9175,7 +10711,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>4</v>
       </c>
@@ -9198,7 +10734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>4</v>
       </c>
@@ -9221,7 +10757,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>4</v>
       </c>
@@ -9244,7 +10780,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -9267,7 +10803,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>4</v>
       </c>
@@ -9290,7 +10826,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>4</v>
       </c>
@@ -9313,7 +10849,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>4</v>
       </c>
@@ -9336,7 +10872,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>4</v>
       </c>
@@ -9359,7 +10895,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>4</v>
       </c>
@@ -9382,7 +10918,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>4</v>
       </c>
@@ -9405,7 +10941,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>4</v>
       </c>
@@ -9428,7 +10964,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>4</v>
       </c>
@@ -9451,7 +10987,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>5</v>
       </c>
@@ -9474,7 +11010,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>5</v>
       </c>
@@ -9497,7 +11033,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>5</v>
       </c>
@@ -9520,7 +11056,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>5</v>
       </c>
@@ -9543,7 +11079,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>5</v>
       </c>
@@ -9566,7 +11102,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>5</v>
       </c>
@@ -9589,7 +11125,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>6</v>
       </c>

--- a/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
@@ -575,19 +575,19 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.0007532999999999999</v>
+        <v>0.0007667</v>
       </c>
       <c r="D2">
-        <v>0.005575500000000001</v>
+        <v>0.005478799999999999</v>
       </c>
       <c r="E2">
-        <v>0.0461979</v>
+        <v>0.0469885</v>
       </c>
       <c r="F2">
-        <v>0.3244957</v>
+        <v>0.3283849</v>
       </c>
       <c r="G2">
-        <v>0.09425559999999999</v>
+        <v>0.095404725</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -598,19 +598,19 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>0.0002836</v>
+        <v>0.0002578</v>
       </c>
       <c r="D3">
-        <v>0.0009771000000000001</v>
+        <v>0.0009590000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0035875</v>
+        <v>0.0038177</v>
       </c>
       <c r="F3">
-        <v>0.0151494</v>
+        <v>0.0159539</v>
       </c>
       <c r="G3">
-        <v>0.004999399999999999</v>
+        <v>0.0052471</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -621,19 +621,19 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>0.0003752</v>
+        <v>0.0004024</v>
       </c>
       <c r="D4">
-        <v>0.001187</v>
+        <v>0.0011576</v>
       </c>
       <c r="E4">
-        <v>0.004454700000000001</v>
+        <v>0.0046085</v>
       </c>
       <c r="F4">
-        <v>0.0222911</v>
+        <v>0.0229427</v>
       </c>
       <c r="G4">
-        <v>0.007077</v>
+        <v>0.0072778</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -644,19 +644,19 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>0.0006342</v>
+        <v>0.0006301</v>
       </c>
       <c r="D5">
-        <v>0.0034419</v>
+        <v>0.003475900000000001</v>
       </c>
       <c r="E5">
-        <v>0.0234846</v>
+        <v>0.022842</v>
       </c>
       <c r="F5">
-        <v>0.15196</v>
+        <v>0.1550188</v>
       </c>
       <c r="G5">
-        <v>0.044880175</v>
+        <v>0.0454917</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -667,19 +667,19 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>0.0006154000000000001</v>
+        <v>0.0006336</v>
       </c>
       <c r="D6">
-        <v>0.0020394</v>
+        <v>0.0021027</v>
       </c>
       <c r="E6">
-        <v>0.007644800000000002</v>
+        <v>0.0078195</v>
       </c>
       <c r="F6">
-        <v>0.0308201</v>
+        <v>0.0307348</v>
       </c>
       <c r="G6">
-        <v>0.010279925</v>
+        <v>0.01032265</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -690,19 +690,19 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>0.0008328999999999999</v>
+        <v>0.0008085</v>
       </c>
       <c r="D7">
-        <v>0.0056887</v>
+        <v>0.005589800000000001</v>
       </c>
       <c r="E7">
-        <v>0.0465208</v>
+        <v>0.0471678</v>
       </c>
       <c r="F7">
-        <v>0.3222724</v>
+        <v>0.335324</v>
       </c>
       <c r="G7">
-        <v>0.0938287</v>
+        <v>0.09722252499999999</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -713,19 +713,19 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>0.0009721</v>
+        <v>0.0009655000000000002</v>
       </c>
       <c r="D8">
-        <v>0.0066259</v>
+        <v>0.006777300000000002</v>
       </c>
       <c r="E8">
-        <v>0.0493103</v>
+        <v>0.0485517</v>
       </c>
       <c r="F8">
-        <v>0.3185250000000001</v>
+        <v>0.3301565</v>
       </c>
       <c r="G8">
-        <v>0.09385832500000002</v>
+        <v>0.09661275</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -736,19 +736,19 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>0.000406</v>
+        <v>0.0004216</v>
       </c>
       <c r="D9">
-        <v>0.0009793</v>
+        <v>0.0009876000000000002</v>
       </c>
       <c r="E9">
-        <v>0.002354600000000001</v>
+        <v>0.0024686</v>
       </c>
       <c r="F9">
-        <v>0.007224899999999999</v>
+        <v>0.0073088</v>
       </c>
       <c r="G9">
-        <v>0.0027412</v>
+        <v>0.00279665</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -759,19 +759,19 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>0.0003239</v>
+        <v>0.0003478999999999999</v>
       </c>
       <c r="D10">
-        <v>0.0012521</v>
+        <v>0.0012983</v>
       </c>
       <c r="E10">
-        <v>0.004901600000000001</v>
+        <v>0.005184199999999999</v>
       </c>
       <c r="F10">
-        <v>0.0210623</v>
+        <v>0.0209648</v>
       </c>
       <c r="G10">
-        <v>0.006884975000000001</v>
+        <v>0.0069488</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -782,19 +782,19 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>0.00027</v>
+        <v>0.0003007</v>
       </c>
       <c r="D11">
-        <v>0.001013</v>
+        <v>0.0010185</v>
       </c>
       <c r="E11">
-        <v>0.0038629</v>
+        <v>0.003979000000000001</v>
       </c>
       <c r="F11">
-        <v>0.0159211</v>
+        <v>0.0162634</v>
       </c>
       <c r="G11">
-        <v>0.005266750000000001</v>
+        <v>0.0053904</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -805,19 +805,19 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>0.0003537</v>
+        <v>0.0003246</v>
       </c>
       <c r="D12">
-        <v>0.0011121</v>
+        <v>0.0010923</v>
       </c>
       <c r="E12">
-        <v>0.0042213</v>
+        <v>0.0042126</v>
       </c>
       <c r="F12">
-        <v>0.0155838</v>
+        <v>0.0157469</v>
       </c>
       <c r="G12">
-        <v>0.005317725000000001</v>
+        <v>0.0053441</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -828,19 +828,19 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>0.0004561</v>
+        <v>0.0004111</v>
       </c>
       <c r="D13">
-        <v>0.0012442</v>
+        <v>0.0013213</v>
       </c>
       <c r="E13">
-        <v>0.0047569</v>
+        <v>0.0048431</v>
       </c>
       <c r="F13">
-        <v>0.0238317</v>
+        <v>0.0236838</v>
       </c>
       <c r="G13">
-        <v>0.007572224999999999</v>
+        <v>0.007564824999999999</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -851,19 +851,19 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>0.0004371</v>
+        <v>0.0004846000000000001</v>
       </c>
       <c r="D14">
-        <v>0.0012875</v>
+        <v>0.0013377</v>
       </c>
       <c r="E14">
-        <v>0.0048975</v>
+        <v>0.0047114</v>
       </c>
       <c r="F14">
-        <v>0.0212835</v>
+        <v>0.021572</v>
       </c>
       <c r="G14">
-        <v>0.0069764</v>
+        <v>0.007026425</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -874,19 +874,19 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>0.0006479999999999999</v>
+        <v>0.0006584</v>
       </c>
       <c r="D15">
-        <v>0.0022117</v>
+        <v>0.0023643</v>
       </c>
       <c r="E15">
-        <v>0.0111786</v>
+        <v>0.0113074</v>
       </c>
       <c r="F15">
-        <v>0.0630918</v>
+        <v>0.06515170000000001</v>
       </c>
       <c r="G15">
-        <v>0.019282525</v>
+        <v>0.01987045</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -897,19 +897,19 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>0.0006506999999999999</v>
+        <v>0.0006569</v>
       </c>
       <c r="D16">
-        <v>0.003600700000000001</v>
+        <v>0.0036338</v>
       </c>
       <c r="E16">
-        <v>0.0233308</v>
+        <v>0.0231579</v>
       </c>
       <c r="F16">
-        <v>0.1549384</v>
+        <v>0.1568437</v>
       </c>
       <c r="G16">
-        <v>0.04563014999999999</v>
+        <v>0.04607307499999999</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -920,19 +920,19 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>0.0005769000000000001</v>
+        <v>0.0006017</v>
       </c>
       <c r="D17">
-        <v>0.0030349</v>
+        <v>0.0030881</v>
       </c>
       <c r="E17">
-        <v>0.0189207</v>
+        <v>0.0193886</v>
       </c>
       <c r="F17">
-        <v>0.1451053</v>
+        <v>0.1476472</v>
       </c>
       <c r="G17">
-        <v>0.04190945</v>
+        <v>0.0426814</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -943,19 +943,19 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>0.0004188</v>
+        <v>0.0004275</v>
       </c>
       <c r="D18">
-        <v>0.0016582</v>
+        <v>0.0017113</v>
       </c>
       <c r="E18">
-        <v>0.0056674</v>
+        <v>0.0058514</v>
       </c>
       <c r="F18">
-        <v>0.0222514</v>
+        <v>0.0224107</v>
       </c>
       <c r="G18">
-        <v>0.007498949999999999</v>
+        <v>0.007600225</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -966,19 +966,19 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>0.0003346999999999999</v>
+        <v>0.0003646</v>
       </c>
       <c r="D19">
-        <v>0.0009968000000000002</v>
+        <v>0.0010013</v>
       </c>
       <c r="E19">
-        <v>0.003597</v>
+        <v>0.0035626</v>
       </c>
       <c r="F19">
-        <v>0.0153414</v>
+        <v>0.0155823</v>
       </c>
       <c r="G19">
-        <v>0.005067475</v>
+        <v>0.0051277</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -989,19 +989,19 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0.0005413999999999999</v>
+        <v>0.0005140000000000001</v>
       </c>
       <c r="D20">
-        <v>0.0017394</v>
+        <v>0.0017887</v>
       </c>
       <c r="E20">
-        <v>0.0062429</v>
+        <v>0.0062539</v>
       </c>
       <c r="F20">
-        <v>0.0237058</v>
+        <v>0.0240745</v>
       </c>
       <c r="G20">
-        <v>0.008057375</v>
+        <v>0.008157774999999999</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1012,19 +1012,19 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>0.0006631</v>
+        <v>0.0006421</v>
       </c>
       <c r="D21">
-        <v>0.002063300000000001</v>
+        <v>0.0020819</v>
       </c>
       <c r="E21">
-        <v>0.007810200000000001</v>
+        <v>0.007710300000000001</v>
       </c>
       <c r="F21">
-        <v>0.0310841</v>
+        <v>0.0308326</v>
       </c>
       <c r="G21">
-        <v>0.010405175</v>
+        <v>0.010316725</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1035,19 +1035,19 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>0.001016</v>
+        <v>0.0010345</v>
       </c>
       <c r="D22">
-        <v>0.0067888</v>
+        <v>0.0067584</v>
       </c>
       <c r="E22">
-        <v>0.0487501</v>
+        <v>0.0479779</v>
       </c>
       <c r="F22">
-        <v>0.3169995</v>
+        <v>0.3336716</v>
       </c>
       <c r="G22">
-        <v>0.0933886</v>
+        <v>0.09736060000000001</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1058,19 +1058,19 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>0.0004487</v>
+        <v>0.0004244</v>
       </c>
       <c r="D23">
-        <v>0.00105</v>
+        <v>0.0010742</v>
       </c>
       <c r="E23">
-        <v>0.0026693</v>
+        <v>0.0027757</v>
       </c>
       <c r="F23">
-        <v>0.0078621</v>
+        <v>0.008041999999999999</v>
       </c>
       <c r="G23">
-        <v>0.003007525</v>
+        <v>0.003079075</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1081,19 +1081,19 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>0.0004038999999999999</v>
+        <v>0.0004507000000000001</v>
       </c>
       <c r="D24">
-        <v>0.0010147</v>
+        <v>0.0010381</v>
       </c>
       <c r="E24">
-        <v>0.0024095</v>
+        <v>0.0026143</v>
       </c>
       <c r="F24">
-        <v>0.0071284</v>
+        <v>0.0070632</v>
       </c>
       <c r="G24">
-        <v>0.002739125</v>
+        <v>0.002791575</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1104,19 +1104,19 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>0.0006615000000000001</v>
+        <v>0.0007115999999999999</v>
       </c>
       <c r="D25">
-        <v>0.0021742</v>
+        <v>0.0022379</v>
       </c>
       <c r="E25">
-        <v>0.007562299999999999</v>
+        <v>0.0077321</v>
       </c>
       <c r="F25">
-        <v>0.0326214</v>
+        <v>0.0334822</v>
       </c>
       <c r="G25">
-        <v>0.01075485</v>
+        <v>0.01104095</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1127,19 +1127,19 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>0.0003611</v>
+        <v>0.0003746</v>
       </c>
       <c r="D26">
-        <v>0.0013935</v>
+        <v>0.0014369</v>
       </c>
       <c r="E26">
-        <v>0.0051702</v>
+        <v>0.0054322</v>
       </c>
       <c r="F26">
-        <v>0.0218238</v>
+        <v>0.0221441</v>
       </c>
       <c r="G26">
-        <v>0.00718715</v>
+        <v>0.00734695</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1150,19 +1150,19 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>0.0003954</v>
+        <v>0.0003779</v>
       </c>
       <c r="D27">
-        <v>0.001401</v>
+        <v>0.0014321</v>
       </c>
       <c r="E27">
-        <v>0.005192199999999999</v>
+        <v>0.005496099999999999</v>
       </c>
       <c r="F27">
-        <v>0.0216025</v>
+        <v>0.0218465</v>
       </c>
       <c r="G27">
-        <v>0.007147775</v>
+        <v>0.007288149999999999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1173,19 +1173,19 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>0.0003712</v>
+        <v>0.0003778</v>
       </c>
       <c r="D28">
-        <v>0.0011419</v>
+        <v>0.0011739</v>
       </c>
       <c r="E28">
-        <v>0.0042606</v>
+        <v>0.004588699999999999</v>
       </c>
       <c r="F28">
-        <v>0.0166567</v>
+        <v>0.0176506</v>
       </c>
       <c r="G28">
-        <v>0.005607600000000001</v>
+        <v>0.00594775</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1196,19 +1196,19 @@
         <v>34</v>
       </c>
       <c r="C29">
-        <v>0.0004908</v>
+        <v>0.0005127</v>
       </c>
       <c r="D29">
-        <v>0.001468</v>
+        <v>0.0014319</v>
       </c>
       <c r="E29">
-        <v>0.0050739</v>
+        <v>0.0049532</v>
       </c>
       <c r="F29">
-        <v>0.0224021</v>
+        <v>0.0239343</v>
       </c>
       <c r="G29">
-        <v>0.0073587</v>
+        <v>0.007708024999999999</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1219,19 +1219,19 @@
         <v>35</v>
       </c>
       <c r="C30">
-        <v>0.0006908000000000001</v>
+        <v>0.0007036</v>
       </c>
       <c r="D30">
-        <v>0.0024577</v>
+        <v>0.002542</v>
       </c>
       <c r="E30">
-        <v>0.011773</v>
+        <v>0.011685</v>
       </c>
       <c r="F30">
-        <v>0.06421289999999999</v>
+        <v>0.06603970000000001</v>
       </c>
       <c r="G30">
-        <v>0.0197836</v>
+        <v>0.020242575</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1242,19 +1242,19 @@
         <v>36</v>
       </c>
       <c r="C31">
-        <v>0.0006861</v>
+        <v>0.0006843</v>
       </c>
       <c r="D31">
-        <v>0.0013812</v>
+        <v>0.001395</v>
       </c>
       <c r="E31">
-        <v>0.005926600000000001</v>
+        <v>0.0059019</v>
       </c>
       <c r="F31">
-        <v>0.0576045</v>
+        <v>0.0599658</v>
       </c>
       <c r="G31">
-        <v>0.0163996</v>
+        <v>0.01698675</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1265,19 +1265,19 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>0.0006221999999999999</v>
+        <v>0.0006719000000000001</v>
       </c>
       <c r="D32">
-        <v>0.0031585</v>
+        <v>0.0031914</v>
       </c>
       <c r="E32">
-        <v>0.0196643</v>
+        <v>0.0198898</v>
       </c>
       <c r="F32">
-        <v>0.1438184</v>
+        <v>0.1497498</v>
       </c>
       <c r="G32">
-        <v>0.04181585</v>
+        <v>0.043375725</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1288,19 +1288,19 @@
         <v>38</v>
       </c>
       <c r="C33">
-        <v>0.0004805</v>
+        <v>0.0004753</v>
       </c>
       <c r="D33">
-        <v>0.0019439</v>
+        <v>0.0019743</v>
       </c>
       <c r="E33">
-        <v>0.006063000000000001</v>
+        <v>0.006159</v>
       </c>
       <c r="F33">
-        <v>0.0236571</v>
+        <v>0.0239718</v>
       </c>
       <c r="G33">
-        <v>0.008036125</v>
+        <v>0.008145100000000001</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1311,19 +1311,19 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>0.0004855000000000001</v>
+        <v>0.0004657</v>
       </c>
       <c r="D34">
-        <v>0.0018658</v>
+        <v>0.0020639</v>
       </c>
       <c r="E34">
-        <v>0.006865399999999999</v>
+        <v>0.006926799999999999</v>
       </c>
       <c r="F34">
-        <v>0.026378</v>
+        <v>0.0263684</v>
       </c>
       <c r="G34">
-        <v>0.008898675</v>
+        <v>0.008956200000000001</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1334,19 +1334,19 @@
         <v>40</v>
       </c>
       <c r="C35">
-        <v>0.0004143</v>
+        <v>0.000424</v>
       </c>
       <c r="D35">
-        <v>0.0017049</v>
+        <v>0.0017545</v>
       </c>
       <c r="E35">
-        <v>0.0058199</v>
+        <v>0.005918999999999999</v>
       </c>
       <c r="F35">
-        <v>0.0221056</v>
+        <v>0.0223174</v>
       </c>
       <c r="G35">
-        <v>0.007511174999999999</v>
+        <v>0.007603724999999999</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1357,19 +1357,19 @@
         <v>41</v>
       </c>
       <c r="C36">
-        <v>0.000372</v>
+        <v>0.0003724999999999999</v>
       </c>
       <c r="D36">
-        <v>0.0010596</v>
+        <v>0.0010814</v>
       </c>
       <c r="E36">
-        <v>0.0036198</v>
+        <v>0.0037438</v>
       </c>
       <c r="F36">
-        <v>0.0157483</v>
+        <v>0.0154254</v>
       </c>
       <c r="G36">
-        <v>0.005199925</v>
+        <v>0.005155775</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1380,19 +1380,19 @@
         <v>42</v>
       </c>
       <c r="C37">
-        <v>0.0003785</v>
+        <v>0.0004047</v>
       </c>
       <c r="D37">
-        <v>0.0010912</v>
+        <v>0.0012488</v>
       </c>
       <c r="E37">
-        <v>0.0035974</v>
+        <v>0.0036319</v>
       </c>
       <c r="F37">
-        <v>0.0131913</v>
+        <v>0.0134449</v>
       </c>
       <c r="G37">
-        <v>0.0045646</v>
+        <v>0.004682575</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1403,19 +1403,19 @@
         <v>43</v>
       </c>
       <c r="C38">
-        <v>0.0005396</v>
+        <v>0.0005528</v>
       </c>
       <c r="D38">
-        <v>0.001772</v>
+        <v>0.0019815</v>
       </c>
       <c r="E38">
-        <v>0.0063563</v>
+        <v>0.0064832</v>
       </c>
       <c r="F38">
-        <v>0.0247923</v>
+        <v>0.0240418</v>
       </c>
       <c r="G38">
-        <v>0.008365050000000001</v>
+        <v>0.008264825</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1426,19 +1426,19 @@
         <v>44</v>
       </c>
       <c r="C39">
-        <v>0.0004877</v>
+        <v>0.0005301</v>
       </c>
       <c r="D39">
-        <v>0.0011211</v>
+        <v>0.0011267</v>
       </c>
       <c r="E39">
-        <v>0.0028354</v>
+        <v>0.0029132</v>
       </c>
       <c r="F39">
-        <v>0.0077328</v>
+        <v>0.0082644</v>
       </c>
       <c r="G39">
-        <v>0.00304425</v>
+        <v>0.0032086</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1449,19 +1449,19 @@
         <v>45</v>
       </c>
       <c r="C40">
-        <v>0.0007149</v>
+        <v>0.0007407</v>
       </c>
       <c r="D40">
-        <v>0.0022341</v>
+        <v>0.0022964</v>
       </c>
       <c r="E40">
-        <v>0.007752300000000001</v>
+        <v>0.008494400000000001</v>
       </c>
       <c r="F40">
-        <v>0.0334018</v>
+        <v>0.0347072</v>
       </c>
       <c r="G40">
-        <v>0.011025775</v>
+        <v>0.011559675</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1472,19 +1472,19 @@
         <v>46</v>
       </c>
       <c r="C41">
-        <v>0.0007580000000000001</v>
+        <v>0.0007589</v>
       </c>
       <c r="D41">
-        <v>0.0022475</v>
+        <v>0.0012024</v>
       </c>
       <c r="E41">
-        <v>0.0035265</v>
+        <v>0.0035316</v>
       </c>
       <c r="F41">
-        <v>0.0293606</v>
+        <v>0.0308734</v>
       </c>
       <c r="G41">
-        <v>0.008973150000000001</v>
+        <v>0.009091575000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1495,19 +1495,19 @@
         <v>47</v>
       </c>
       <c r="C42">
-        <v>0.0004213</v>
+        <v>0.0006334</v>
       </c>
       <c r="D42">
-        <v>0.0015082</v>
+        <v>0.0015849</v>
       </c>
       <c r="E42">
-        <v>0.005455799999999999</v>
+        <v>0.0058336</v>
       </c>
       <c r="F42">
-        <v>0.0224559</v>
+        <v>0.0229308</v>
       </c>
       <c r="G42">
-        <v>0.0074603</v>
+        <v>0.007745674999999999</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1518,19 +1518,19 @@
         <v>48</v>
       </c>
       <c r="C43">
-        <v>0.0007337</v>
+        <v>0.0007381</v>
       </c>
       <c r="D43">
-        <v>0.001422</v>
+        <v>0.0014534</v>
       </c>
       <c r="E43">
-        <v>0.006362700000000001</v>
+        <v>0.006205099999999999</v>
       </c>
       <c r="F43">
-        <v>0.058849</v>
+        <v>0.06062149999999999</v>
       </c>
       <c r="G43">
-        <v>0.01684185</v>
+        <v>0.017254525</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1541,19 +1541,19 @@
         <v>49</v>
       </c>
       <c r="C44">
-        <v>0.0005090000000000001</v>
+        <v>0.0005218</v>
       </c>
       <c r="D44">
-        <v>0.0020739</v>
+        <v>0.0019859</v>
       </c>
       <c r="E44">
-        <v>0.0062131</v>
+        <v>0.0063473</v>
       </c>
       <c r="F44">
-        <v>0.0239144</v>
+        <v>0.0240816</v>
       </c>
       <c r="G44">
-        <v>0.0081776</v>
+        <v>0.008234150000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1564,19 +1564,19 @@
         <v>50</v>
       </c>
       <c r="C45">
-        <v>0.0004572000000000001</v>
+        <v>0.0004489</v>
       </c>
       <c r="D45">
-        <v>0.0020809</v>
+        <v>0.002095</v>
       </c>
       <c r="E45">
-        <v>0.006483</v>
+        <v>0.0066298</v>
       </c>
       <c r="F45">
-        <v>0.0247118</v>
+        <v>0.0249727</v>
       </c>
       <c r="G45">
-        <v>0.008433224999999999</v>
+        <v>0.008536599999999998</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1587,19 +1587,19 @@
         <v>51</v>
       </c>
       <c r="C46">
-        <v>0.0004902</v>
+        <v>0.0005264</v>
       </c>
       <c r="D46">
-        <v>0.0019476</v>
+        <v>0.0019705</v>
       </c>
       <c r="E46">
-        <v>0.007005199999999999</v>
+        <v>0.006997099999999999</v>
       </c>
       <c r="F46">
-        <v>0.0265213</v>
+        <v>0.0271384</v>
       </c>
       <c r="G46">
-        <v>0.008991075000000001</v>
+        <v>0.009158099999999999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1610,19 +1610,19 @@
         <v>52</v>
       </c>
       <c r="C47">
-        <v>0.0004404</v>
+        <v>0.0004162</v>
       </c>
       <c r="D47">
-        <v>0.0013578</v>
+        <v>0.0013113</v>
       </c>
       <c r="E47">
-        <v>0.0036425</v>
+        <v>0.003739000000000001</v>
       </c>
       <c r="F47">
-        <v>0.0136352</v>
+        <v>0.0132889</v>
       </c>
       <c r="G47">
-        <v>0.004768975</v>
+        <v>0.00468885</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1633,19 +1633,19 @@
         <v>53</v>
       </c>
       <c r="C48">
-        <v>0.0007973000000000001</v>
+        <v>0.0008023</v>
       </c>
       <c r="D48">
-        <v>0.0016125</v>
+        <v>0.0013203</v>
       </c>
       <c r="E48">
-        <v>0.0037</v>
+        <v>0.003867300000000001</v>
       </c>
       <c r="F48">
-        <v>0.0310981</v>
+        <v>0.0325025</v>
       </c>
       <c r="G48">
-        <v>0.009301975000000001</v>
+        <v>0.009623100000000001</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1656,19 +1656,19 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>0.0004685</v>
+        <v>0.0005008</v>
       </c>
       <c r="D49">
-        <v>0.0021003</v>
+        <v>0.0021206</v>
       </c>
       <c r="E49">
-        <v>0.0065944</v>
+        <v>0.006773</v>
       </c>
       <c r="F49">
-        <v>0.0247399</v>
+        <v>0.025712</v>
       </c>
       <c r="G49">
-        <v>0.008475775</v>
+        <v>0.008776600000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0007653</v>
+        <v>0.0007156</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0055339</v>
+        <v>0.0055638</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0473926</v>
+        <v>0.0476005</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3204569999999999</v>
+        <v>0.3275252</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09353719999999999</v>
+        <v>0.095351275</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002525</v>
+        <v>0.0002566</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009266</v>
+        <v>0.000949</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00377</v>
+        <v>0.0036597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0151109</v>
+        <v>0.0152924</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005015</v>
+        <v>0.005039425</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.000434</v>
+        <v>0.0004205</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0011927</v>
+        <v>0.0010958</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0045225</v>
+        <v>0.004232499999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0221792</v>
+        <v>0.0183858</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007082100000000001</v>
+        <v>0.00603365</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0006855</v>
+        <v>0.0005861</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0035036</v>
+        <v>0.0035187</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0225131</v>
+        <v>0.0229887</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1538694</v>
+        <v>0.1579327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0451429</v>
+        <v>0.04625655</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0006127000000000001</v>
+        <v>0.0006101</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0021129</v>
+        <v>0.0020775</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007730100000000001</v>
+        <v>0.0075617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0314106</v>
+        <v>0.03146120000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.010466575</v>
+        <v>0.010427625</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0008480000000000001</v>
+        <v>0.0007934</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0055068</v>
+        <v>0.0056369</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0472964</v>
+        <v>0.04769320000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3219922000000001</v>
+        <v>0.3320585</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09391085000000002</v>
+        <v>0.09654549999999999</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0010152</v>
+        <v>0.0009327000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006709700000000001</v>
+        <v>0.0067103</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0470782</v>
+        <v>0.04839880000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.321169</v>
+        <v>0.3265101</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09399302499999999</v>
+        <v>0.09563797499999999</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0004145</v>
+        <v>0.0004056</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009712</v>
+        <v>0.0010508</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0023633</v>
+        <v>0.0026066</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0072241</v>
+        <v>0.007560800000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002743275</v>
+        <v>0.00290595</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003248</v>
+        <v>0.0003405</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0012621</v>
+        <v>0.0012473</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0050688</v>
+        <v>0.0051008</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0205669</v>
+        <v>0.0211359</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00680565</v>
+        <v>0.006956125000000001</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.000289</v>
+        <v>0.0002846</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0010516</v>
+        <v>0.0010389</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0038884</v>
+        <v>0.0039076</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0165612</v>
+        <v>0.0164304</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005447550000000001</v>
+        <v>0.005415375</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003321</v>
+        <v>0.0003301000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>0.0010739</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004163399999999999</v>
+        <v>0.004059200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0155419</v>
+        <v>0.015643</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005277825</v>
+        <v>0.005276550000000001</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0003888</v>
+        <v>0.0004326999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001315</v>
+        <v>0.0011746</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0048621</v>
+        <v>0.0045699</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0237085</v>
+        <v>0.0195259</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0075686</v>
+        <v>0.006425775000000001</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004434</v>
+        <v>0.0004272</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0013096</v>
+        <v>0.0011982</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0045958</v>
+        <v>0.0043693</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0213892</v>
+        <v>0.0203732</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0069345</v>
+        <v>0.006591975</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.000638</v>
+        <v>0.0005328</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0023044</v>
+        <v>0.0013076</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0110343</v>
+        <v>0.0044917</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06314119999999999</v>
+        <v>0.0327703</v>
       </c>
       <c r="G15" t="n">
-        <v>0.019279475</v>
+        <v>0.009775600000000001</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000637</v>
+        <v>0.0006322000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0035848</v>
+        <v>0.0036029</v>
       </c>
       <c r="E16" t="n">
-        <v>0.022946</v>
+        <v>0.0235995</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1529413</v>
+        <v>0.1580801</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04502727499999999</v>
+        <v>0.046478675</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005796</v>
+        <v>0.0005668</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0031633</v>
+        <v>0.0030473</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0188285</v>
+        <v>0.0195492</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1432563</v>
+        <v>0.1488626</v>
       </c>
       <c r="G17" t="n">
-        <v>0.041456925</v>
+        <v>0.043006475</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.000415</v>
+        <v>0.0003853</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0015677</v>
+        <v>0.0015601</v>
       </c>
       <c r="E18" t="n">
-        <v>0.005627499999999999</v>
+        <v>0.0057353</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0225995</v>
+        <v>0.0224186</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007552425</v>
+        <v>0.007524825000000001</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0003425</v>
+        <v>0.0002904</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0010957</v>
+        <v>0.0011592</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0035537</v>
+        <v>0.0034086</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0161645</v>
+        <v>0.0131264</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0052891</v>
+        <v>0.004496150000000001</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005146</v>
+        <v>0.0005181000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0018555</v>
+        <v>0.0017371</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0061916</v>
+        <v>0.006408899999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0236826</v>
+        <v>0.0241837</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008061075000000001</v>
+        <v>0.008211949999999999</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0006307</v>
+        <v>0.0006422000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0023425</v>
+        <v>0.0021</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0077269</v>
+        <v>0.0076461</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0317753</v>
+        <v>0.0317962</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01061885</v>
+        <v>0.010546125</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0010021</v>
+        <v>0.001004</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0067299</v>
+        <v>0.007885</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0475462</v>
+        <v>0.0490782</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3195069</v>
+        <v>0.3309083</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09369627500000001</v>
+        <v>0.097218875</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000415</v>
+        <v>0.0004478</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0010406</v>
+        <v>0.001113</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0026075</v>
+        <v>0.0028218</v>
       </c>
       <c r="F23" t="n">
-        <v>0.007937400000000001</v>
+        <v>0.008396400000000002</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003000125</v>
+        <v>0.003194750000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004327</v>
+        <v>0.0004641</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0010559</v>
+        <v>0.0011287</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0024966</v>
+        <v>0.0028351</v>
       </c>
       <c r="F24" t="n">
-        <v>0.007165599999999999</v>
+        <v>0.0081403</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0027877</v>
+        <v>0.00314205</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0007077</v>
+        <v>0.0005700999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0021807</v>
+        <v>0.00114</v>
       </c>
       <c r="E25" t="n">
-        <v>0.007592699999999999</v>
+        <v>0.003362900000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0330019</v>
+        <v>0.0138207</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01087075</v>
+        <v>0.004723425</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003699999999999999</v>
+        <v>0.0003511</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0013304</v>
+        <v>0.0013239</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0051287</v>
+        <v>0.005453700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.022497</v>
+        <v>0.0222523</v>
       </c>
       <c r="G26" t="n">
-        <v>0.007331525</v>
+        <v>0.00734525</v>
       </c>
     </row>
     <row r="27">
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003649</v>
+        <v>0.0003752</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0015489</v>
+        <v>0.0014419</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0052375</v>
+        <v>0.005398999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0216638</v>
+        <v>0.0218032</v>
       </c>
       <c r="G27" t="n">
-        <v>0.007203775</v>
+        <v>0.007254825</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003686</v>
+        <v>0.0003599000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0011686</v>
+        <v>0.0011633</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0044796</v>
+        <v>0.0044339</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0167846</v>
+        <v>0.01711</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005700350000000001</v>
+        <v>0.005766774999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0005001000000000001</v>
+        <v>0.0004694</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0013675</v>
+        <v>0.0012645</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0049241</v>
+        <v>0.0046141</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0228962</v>
+        <v>0.0213946</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007421975</v>
+        <v>0.006935650000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0006698</v>
+        <v>0.0005954000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0023649</v>
+        <v>0.0013362</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0114502</v>
+        <v>0.0047093</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06477459999999999</v>
+        <v>0.03408899999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>0.019814875</v>
+        <v>0.010182475</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0006980999999999999</v>
+        <v>0.0006293000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0013723</v>
+        <v>0.00129</v>
       </c>
       <c r="E31" t="n">
-        <v>0.005919299999999999</v>
+        <v>0.0042204</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0587969</v>
+        <v>0.0360269</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01669665</v>
+        <v>0.01054165</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0006175999999999999</v>
+        <v>0.000607</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0032764</v>
+        <v>0.0031782</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0190991</v>
+        <v>0.0195168</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1435159</v>
+        <v>0.1492431</v>
       </c>
       <c r="G32" t="n">
-        <v>0.04162724999999999</v>
+        <v>0.043136275</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0004666</v>
+        <v>0.0003457999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0019665</v>
+        <v>0.0019938</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0060623</v>
+        <v>0.006326099999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0239241</v>
+        <v>0.0258252</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008104875000000001</v>
+        <v>0.008622724999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0004754</v>
+        <v>0.0004891</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0019586</v>
+        <v>0.0020816</v>
       </c>
       <c r="E34" t="n">
-        <v>0.007007200000000001</v>
+        <v>0.006866300000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.026464</v>
+        <v>0.0268445</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0089763</v>
+        <v>0.009070375</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0004458</v>
+        <v>0.0004442999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0015955</v>
+        <v>0.0016444</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0057473</v>
+        <v>0.005908200000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0224728</v>
+        <v>0.02281</v>
       </c>
       <c r="G35" t="n">
-        <v>0.007565350000000001</v>
+        <v>0.007701725</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0003879</v>
+        <v>0.000339</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0011545</v>
+        <v>0.0011946</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0035898</v>
+        <v>0.0034093</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0154717</v>
+        <v>0.0131543</v>
       </c>
       <c r="G36" t="n">
-        <v>0.005150975</v>
+        <v>0.0045243</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0004047</v>
+        <v>0.0003591000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0010924</v>
+        <v>0.0010907</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0035476</v>
+        <v>0.0035996</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0134771</v>
+        <v>0.0136828</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00463045</v>
+        <v>0.00468305</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0005396999999999999</v>
+        <v>0.0005572999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0019108</v>
+        <v>0.001806</v>
       </c>
       <c r="E38" t="n">
-        <v>0.006250700000000001</v>
+        <v>0.0062168</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0237722</v>
+        <v>0.0244056</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00811835</v>
+        <v>0.008246425</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0004946</v>
+        <v>0.0004466</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0011235</v>
+        <v>0.0012492</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0027776</v>
+        <v>0.0030373</v>
       </c>
       <c r="F39" t="n">
-        <v>0.007779799999999999</v>
+        <v>0.009071300000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>0.003043875</v>
+        <v>0.0034511</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0007017</v>
+        <v>0.0006461999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0026861</v>
+        <v>0.0012489</v>
       </c>
       <c r="E40" t="n">
-        <v>0.007861400000000001</v>
+        <v>0.0036216</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0339216</v>
+        <v>0.0145101</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0112927</v>
+        <v>0.0050067</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0007413000000000001</v>
+        <v>0.0006454000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0019854</v>
+        <v>0.0012132</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0034258</v>
+        <v>0.0036287</v>
       </c>
       <c r="F41" t="n">
-        <v>0.02993669999999999</v>
+        <v>0.0120211</v>
       </c>
       <c r="G41" t="n">
-        <v>0.009022299999999999</v>
+        <v>0.0043771</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0004111999999999999</v>
+        <v>0.0004918</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0015291</v>
+        <v>0.0014965</v>
       </c>
       <c r="E42" t="n">
-        <v>0.005654999999999999</v>
+        <v>0.0057905</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0224874</v>
+        <v>0.0230931</v>
       </c>
       <c r="G42" t="n">
-        <v>0.007520674999999999</v>
+        <v>0.007717975</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0007242</v>
+        <v>0.0006453</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0014775</v>
+        <v>0.0013504</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0061249</v>
+        <v>0.004421</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0594894</v>
+        <v>0.0369717</v>
       </c>
       <c r="G43" t="n">
-        <v>0.016954</v>
+        <v>0.0108471</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0004723</v>
+        <v>0.0003664</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0019653</v>
+        <v>0.0019892</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006134199999999999</v>
+        <v>0.006336800000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0238584</v>
+        <v>0.0257075</v>
       </c>
       <c r="G44" t="n">
-        <v>0.00810755</v>
+        <v>0.008599975000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004513000000000001</v>
+        <v>0.0004005</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0020663</v>
+        <v>0.001986299999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>0.006576599999999999</v>
+        <v>0.0068523</v>
       </c>
       <c r="F45" t="n">
-        <v>0.024905</v>
+        <v>0.0248899</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0084998</v>
+        <v>0.00853225</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0004824</v>
+        <v>0.0004878</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0019724</v>
+        <v>0.0020998</v>
       </c>
       <c r="E46" t="n">
-        <v>0.006897200000000001</v>
+        <v>0.006909800000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0263109</v>
+        <v>0.0266316</v>
       </c>
       <c r="G46" t="n">
-        <v>0.008915724999999999</v>
+        <v>0.009032249999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0004026</v>
+        <v>0.0003775</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0012054</v>
+        <v>0.0011277</v>
       </c>
       <c r="E47" t="n">
-        <v>0.003625</v>
+        <v>0.0037401</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0133908</v>
+        <v>0.0138309</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00465595</v>
+        <v>0.00476905</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0007620000000000001</v>
+        <v>0.0007030999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001364</v>
+        <v>0.0013255</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0036326</v>
+        <v>0.0035712</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0312175</v>
+        <v>0.0130827</v>
       </c>
       <c r="G48" t="n">
-        <v>0.009244024999999999</v>
+        <v>0.004670624999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004543</v>
+        <v>0.0004228000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0020277</v>
+        <v>0.0020322</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0066388</v>
+        <v>0.0066852</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0244447</v>
+        <v>0.0254287</v>
       </c>
       <c r="G49" t="n">
-        <v>0.008391375</v>
+        <v>0.008642225</v>
       </c>
     </row>
   </sheetData>
@@ -1810,16 +1810,16 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="G4" t="n">
-        <v>86.75</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="5">
@@ -1938,13 +1938,13 @@
         <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -2057,19 +2057,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F14" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G14" t="n">
-        <v>86.25</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="15">
@@ -2085,16 +2085,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F15" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G15" t="n">
-        <v>85.75</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="16">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -2244,7 +2244,7 @@
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2316,10 +2316,10 @@
         <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G24" t="n">
-        <v>75.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25">
@@ -2335,16 +2335,16 @@
         <v>21</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="F25" t="n">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="G25" t="n">
-        <v>85.75</v>
+        <v>78.25</v>
       </c>
     </row>
     <row r="26">
@@ -2357,19 +2357,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>6</v>
@@ -2469,7 +2469,7 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="31">
@@ -2485,16 +2485,16 @@
         <v>21</v>
       </c>
       <c r="D31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F31" t="n">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="G31" t="n">
-        <v>82.75</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="32">
@@ -2538,13 +2538,13 @@
         <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
         <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
         <v>4</v>
@@ -2594,7 +2594,7 @@
         <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -2610,16 +2610,16 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="37">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
         <v>4</v>
@@ -2669,7 +2669,7 @@
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
         <v>6</v>
@@ -2719,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="41">
@@ -2738,13 +2738,13 @@
         <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F41" t="n">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="G41" t="n">
-        <v>81.75</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="42">
@@ -2757,19 +2757,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
         <v>6</v>
@@ -2794,7 +2794,7 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="44">
@@ -2810,16 +2810,16 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="45">
@@ -2835,7 +2835,7 @@
         <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
         <v>16</v>
@@ -2844,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="G45" t="n">
-        <v>14.75</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46">
@@ -2857,19 +2857,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -2885,16 +2885,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="48">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
         <v>6</v>
@@ -2919,7 +2919,7 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="49">
@@ -2935,16 +2935,16 @@
         <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>
@@ -3061,16 +3061,16 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D4" t="n">
-        <v>50.87005768508881</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E4" t="n">
-        <v>106.0832611206852</v>
+        <v>103.7401153701776</v>
       </c>
       <c r="F4" t="n">
-        <v>215.9238815542512</v>
+        <v>208.8944443027283</v>
       </c>
       <c r="G4" t="n">
-        <v>99.10838738653231</v>
+        <v>96.17945519839779</v>
       </c>
     </row>
     <row r="5">
@@ -3189,13 +3189,13 @@
         <v>48.52691193458118</v>
       </c>
       <c r="E9" t="n">
-        <v>99.63961030678929</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F9" t="n">
-        <v>201.8650070512055</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="G9" t="n">
-        <v>93.39696961967</v>
+        <v>92.63961030678928</v>
       </c>
     </row>
     <row r="10">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.57753044284504</v>
+        <v>22.52857279783051</v>
       </c>
       <c r="D13" t="n">
-        <v>47.74928644209569</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E13" t="n">
-        <v>95.98874136669238</v>
+        <v>95.97749958777082</v>
       </c>
       <c r="F13" t="n">
-        <v>193.9130185765683</v>
+        <v>193.9074207545753</v>
       </c>
       <c r="G13" t="n">
-        <v>90.05714420705036</v>
+        <v>89.66858848991086</v>
       </c>
     </row>
     <row r="14">
@@ -3308,19 +3308,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.72792206135785</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="D14" t="n">
-        <v>52.04163056034262</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E14" t="n">
-        <v>105.4974746830583</v>
+        <v>103.1543289325507</v>
       </c>
       <c r="F14" t="n">
-        <v>212.9949493661166</v>
+        <v>208.8944443027283</v>
       </c>
       <c r="G14" t="n">
-        <v>98.81549416771885</v>
+        <v>96.03300858899107</v>
       </c>
     </row>
     <row r="15">
@@ -3336,16 +3336,16 @@
         <v>24.97056274847714</v>
       </c>
       <c r="D15" t="n">
-        <v>52.87005768508881</v>
+        <v>49.1126983722081</v>
       </c>
       <c r="E15" t="n">
-        <v>107.1543289325507</v>
+        <v>100.8111831820431</v>
       </c>
       <c r="F15" t="n">
-        <v>215.7228714274746</v>
+        <v>215.4802307403552</v>
       </c>
       <c r="G15" t="n">
-        <v>100.1794551983978</v>
+        <v>97.5936687607709</v>
       </c>
     </row>
     <row r="16">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.20937271229855</v>
+        <v>22.97056274847714</v>
       </c>
       <c r="D21" t="n">
         <v>47.01219330881975</v>
@@ -3495,7 +3495,7 @@
         <v>191.5449991519585</v>
       </c>
       <c r="G21" t="n">
-        <v>88.98646867694093</v>
+        <v>89.17676618598557</v>
       </c>
     </row>
     <row r="22">
@@ -3533,19 +3533,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.57753044284504</v>
+        <v>22.52857279783051</v>
       </c>
       <c r="D23" t="n">
-        <v>46.28372024631943</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E23" t="n">
-        <v>93.77108547621511</v>
+        <v>93.75984369729352</v>
       </c>
       <c r="F23" t="n">
-        <v>188.7776096300709</v>
+        <v>188.7720118080779</v>
       </c>
       <c r="G23" t="n">
-        <v>87.85248644886262</v>
+        <v>87.83032228066719</v>
       </c>
     </row>
     <row r="24">
@@ -3564,13 +3564,13 @@
         <v>48.52691193458118</v>
       </c>
       <c r="E24" t="n">
-        <v>98.46803743153546</v>
+        <v>99.29646455628166</v>
       </c>
       <c r="F24" t="n">
-        <v>198.9360748630709</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G24" t="n">
-        <v>92.3718433538229</v>
+        <v>92.43250352560273</v>
       </c>
     </row>
     <row r="25">
@@ -3586,16 +3586,16 @@
         <v>24.97056274847714</v>
       </c>
       <c r="D25" t="n">
-        <v>52.87005768508881</v>
+        <v>49.94112549695429</v>
       </c>
       <c r="E25" t="n">
-        <v>106.3259018078045</v>
+        <v>100.2253967444162</v>
       </c>
       <c r="F25" t="n">
-        <v>213.2375900532359</v>
+        <v>203.8650070512055</v>
       </c>
       <c r="G25" t="n">
-        <v>99.35102807365161</v>
+        <v>94.75052301026329</v>
       </c>
     </row>
     <row r="26">
@@ -3608,19 +3608,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.96165602967598</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D26" t="n">
-        <v>46.78517569143533</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E26" t="n">
-        <v>94.56434260829852</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F26" t="n">
-        <v>190.172921975932</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="G26" t="n">
-        <v>88.62102407633546</v>
+        <v>88.53498363552973</v>
       </c>
     </row>
     <row r="27">
@@ -3683,19 +3683,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22.93019369378658</v>
+        <v>22.52857279783051</v>
       </c>
       <c r="D29" t="n">
-        <v>47.74928644209569</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E29" t="n">
-        <v>95.98874136669238</v>
+        <v>95.97749958777082</v>
       </c>
       <c r="F29" t="n">
-        <v>193.9130185765683</v>
+        <v>193.9074207545753</v>
       </c>
       <c r="G29" t="n">
-        <v>90.14531001978574</v>
+        <v>89.66858848991086</v>
       </c>
     </row>
     <row r="30">
@@ -3708,19 +3708,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.76409195040512</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D30" t="n">
-        <v>48.63198754963837</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E30" t="n">
-        <v>98.33754137478607</v>
+        <v>93.8728585920724</v>
       </c>
       <c r="F30" t="n">
-        <v>197.8050551315116</v>
+        <v>192.1148020630235</v>
       </c>
       <c r="G30" t="n">
-        <v>92.13466900158528</v>
+        <v>88.77645555917422</v>
       </c>
     </row>
     <row r="31">
@@ -3736,16 +3736,16 @@
         <v>24.97056274847714</v>
       </c>
       <c r="D31" t="n">
-        <v>49.1126983722081</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E31" t="n">
-        <v>101.39696961967</v>
+        <v>99.05382386916236</v>
       </c>
       <c r="F31" t="n">
-        <v>212.4091629284898</v>
+        <v>202.4507934888324</v>
       </c>
       <c r="G31" t="n">
-        <v>96.97234841721126</v>
+        <v>93.75052301026327</v>
       </c>
     </row>
     <row r="32">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>21.78638427399124</v>
+        <v>22.52730043086546</v>
       </c>
       <c r="D35" t="n">
         <v>46.02417147054884</v>
@@ -3845,7 +3845,7 @@
         <v>187.3439890251819</v>
       </c>
       <c r="G35" t="n">
-        <v>87.0681506715672</v>
+        <v>87.25337971078574</v>
       </c>
     </row>
     <row r="36">
@@ -3858,19 +3858,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22.89272449162535</v>
+        <v>22.84376684661083</v>
       </c>
       <c r="D36" t="n">
-        <v>47.12832144194294</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E36" t="n">
-        <v>95.50992475463946</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F36" t="n">
-        <v>192.2919197484023</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="G36" t="n">
-        <v>89.4557226091525</v>
+        <v>88.53160015664891</v>
       </c>
     </row>
     <row r="37">
@@ -3908,7 +3908,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>22.20937271229855</v>
+        <v>22.97056274847714</v>
       </c>
       <c r="D38" t="n">
         <v>47.01219330881975</v>
@@ -3920,7 +3920,7 @@
         <v>191.5449991519585</v>
       </c>
       <c r="G38" t="n">
-        <v>88.98646867694093</v>
+        <v>89.17676618598557</v>
       </c>
     </row>
     <row r="39">
@@ -3933,19 +3933,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>22.57753044284504</v>
+        <v>22.84376684661083</v>
       </c>
       <c r="D39" t="n">
-        <v>46.28372024631943</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E39" t="n">
-        <v>93.77108547621511</v>
+        <v>93.75984369729352</v>
       </c>
       <c r="F39" t="n">
-        <v>188.7776096300709</v>
+        <v>188.7720118080779</v>
       </c>
       <c r="G39" t="n">
-        <v>87.85248644886262</v>
+        <v>87.90912079286227</v>
       </c>
     </row>
     <row r="40">
@@ -3958,19 +3958,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23.62847639896459</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D40" t="n">
-        <v>48.77283648749818</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E40" t="n">
-        <v>98.33004151230152</v>
+        <v>93.75984369729352</v>
       </c>
       <c r="F40" t="n">
-        <v>197.8007181052097</v>
+        <v>188.7720118080779</v>
       </c>
       <c r="G40" t="n">
-        <v>92.13301812599349</v>
+        <v>87.91250427174307</v>
       </c>
     </row>
     <row r="41">
@@ -3989,13 +3989,13 @@
         <v>48.52691193458118</v>
       </c>
       <c r="E41" t="n">
-        <v>99.63961030678929</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F41" t="n">
-        <v>213.2375900532359</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G41" t="n">
-        <v>96.5936687607709</v>
+        <v>92.57895013500945</v>
       </c>
     </row>
     <row r="42">
@@ -4008,19 +4008,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>22.96165602967598</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D42" t="n">
-        <v>46.78517569143533</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E42" t="n">
-        <v>94.56434260829852</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F42" t="n">
-        <v>190.172921975932</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="G42" t="n">
-        <v>88.62102407633546</v>
+        <v>88.53498363552973</v>
       </c>
     </row>
     <row r="43">
@@ -4033,19 +4033,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>23.76409195040512</v>
+        <v>22.99699583160862</v>
       </c>
       <c r="D43" t="n">
-        <v>46.4321335300351</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E43" t="n">
-        <v>94.22101270140124</v>
+        <v>93.8728585920724</v>
       </c>
       <c r="F43" t="n">
-        <v>197.9000825359283</v>
+        <v>189.9438919833272</v>
       </c>
       <c r="G43" t="n">
-        <v>90.57933017944244</v>
+        <v>88.26865180661878</v>
       </c>
     </row>
     <row r="44">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23.85486567281982</v>
+        <v>23.80590802780531</v>
       </c>
       <c r="D44" t="n">
-        <v>47.71474284512288</v>
+        <v>47.62902808688504</v>
       </c>
       <c r="E44" t="n">
-        <v>96.35556830690527</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F44" t="n">
-        <v>193.6796396249865</v>
+        <v>193.604162987165</v>
       </c>
       <c r="G44" t="n">
-        <v>90.40120411245863</v>
+        <v>89.88120665263305</v>
       </c>
     </row>
     <row r="45">
@@ -4108,19 +4108,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>22.96165602967598</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D46" t="n">
-        <v>47.71474284512288</v>
+        <v>47.62902808688504</v>
       </c>
       <c r="E46" t="n">
-        <v>95.50992475463946</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F46" t="n">
-        <v>192.2919197484023</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="G46" t="n">
-        <v>89.61956084446015</v>
+        <v>88.76737542395162</v>
       </c>
     </row>
     <row r="47">
@@ -4133,19 +4133,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22.89272449162535</v>
+        <v>22.84376684661083</v>
       </c>
       <c r="D47" t="n">
-        <v>47.12832144194294</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E47" t="n">
-        <v>95.50992475463946</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F47" t="n">
-        <v>192.2919197484023</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="G47" t="n">
-        <v>89.4557226091525</v>
+        <v>88.53160015664891</v>
       </c>
     </row>
     <row r="48">
@@ -4158,19 +4158,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>23.62847639896459</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D48" t="n">
-        <v>46.28372024631943</v>
+        <v>46.26086081946685</v>
       </c>
       <c r="E48" t="n">
-        <v>93.77108547621511</v>
+        <v>93.75984369729352</v>
       </c>
       <c r="F48" t="n">
-        <v>197.8007181052097</v>
+        <v>188.7720118080779</v>
       </c>
       <c r="G48" t="n">
-        <v>90.3710000566772</v>
+        <v>87.91250427174307</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>23.85486567281982</v>
+        <v>23.80590802780531</v>
       </c>
       <c r="D49" t="n">
-        <v>47.71474284512288</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E49" t="n">
-        <v>95.50992475463946</v>
+        <v>94.48572750867693</v>
       </c>
       <c r="F49" t="n">
-        <v>192.2919197484023</v>
+        <v>190.0974453381104</v>
       </c>
       <c r="G49" t="n">
-        <v>89.8428632552461</v>
+        <v>88.77213545194753</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F4" t="n">
-        <v>469</v>
+        <v>565</v>
       </c>
       <c r="G4" t="n">
-        <v>203.5</v>
+        <v>236.25</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E9" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="F9" t="n">
-        <v>524</v>
+        <v>616</v>
       </c>
       <c r="G9" t="n">
-        <v>228.75</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="F13" t="n">
-        <v>469</v>
+        <v>565</v>
       </c>
       <c r="G13" t="n">
-        <v>203.5</v>
+        <v>236.25</v>
       </c>
     </row>
     <row r="14">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E14" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="F14" t="n">
-        <v>458</v>
+        <v>594</v>
       </c>
       <c r="G14" t="n">
-        <v>201.75</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
@@ -4587,16 +4587,16 @@
         <v>46</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="F15" t="n">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="G15" t="n">
-        <v>260</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="16">
@@ -4684,19 +4684,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="20">
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E23" t="n">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="F23" t="n">
-        <v>524</v>
+        <v>616</v>
       </c>
       <c r="G23" t="n">
-        <v>228.75</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24">
@@ -4809,19 +4809,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E24" t="n">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="F24" t="n">
-        <v>489</v>
+        <v>606</v>
       </c>
       <c r="G24" t="n">
-        <v>216</v>
+        <v>255.5</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D25" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E25" t="n">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="F25" t="n">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="G25" t="n">
-        <v>261</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="26">
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D29" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E29" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="F29" t="n">
-        <v>458</v>
+        <v>594</v>
       </c>
       <c r="G29" t="n">
-        <v>201.75</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30">
@@ -4962,16 +4962,16 @@
         <v>46</v>
       </c>
       <c r="D30" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E30" t="n">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="F30" t="n">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="G30" t="n">
-        <v>260</v>
+        <v>237.5</v>
       </c>
     </row>
     <row r="31">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D31" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E31" t="n">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="F31" t="n">
-        <v>605</v>
+        <v>556</v>
       </c>
       <c r="G31" t="n">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
         <v>16</v>
       </c>
       <c r="E33" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" t="n">
         <v>15</v>
-      </c>
-      <c r="F33" t="n">
-        <v>15</v>
-      </c>
-      <c r="G33" t="n">
-        <v>14.75</v>
       </c>
     </row>
     <row r="34">
@@ -5109,19 +5109,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
         <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="37">
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
         <v>9</v>
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D39" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E39" t="n">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="F39" t="n">
-        <v>489</v>
+        <v>606</v>
       </c>
       <c r="G39" t="n">
-        <v>216</v>
+        <v>255.5</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D40" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E40" t="n">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="F40" t="n">
-        <v>589</v>
+        <v>619</v>
       </c>
       <c r="G40" t="n">
-        <v>261</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D41" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E41" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F41" t="n">
-        <v>676</v>
+        <v>632</v>
       </c>
       <c r="G41" t="n">
-        <v>275.75</v>
+        <v>267.5</v>
       </c>
     </row>
     <row r="42">
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D43" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E43" t="n">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="F43" t="n">
-        <v>605</v>
+        <v>556</v>
       </c>
       <c r="G43" t="n">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44">
@@ -5309,19 +5309,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
         <v>16</v>
       </c>
       <c r="E44" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" t="n">
+        <v>16</v>
+      </c>
+      <c r="G44" t="n">
         <v>15</v>
-      </c>
-      <c r="F44" t="n">
-        <v>15</v>
-      </c>
-      <c r="G44" t="n">
-        <v>14.75</v>
       </c>
     </row>
     <row r="45">
@@ -5337,7 +5337,7 @@
         <v>12</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
         <v>18</v>
@@ -5346,7 +5346,7 @@
         <v>18</v>
       </c>
       <c r="G45" t="n">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="46">
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
         <v>9</v>
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E48" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F48" t="n">
-        <v>676</v>
+        <v>632</v>
       </c>
       <c r="G48" t="n">
-        <v>275.75</v>
+        <v>267.5</v>
       </c>
     </row>
     <row r="49">
@@ -5437,7 +5437,7 @@
         <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E49" t="n">
         <v>18</v>
@@ -5446,7 +5446,7 @@
         <v>18</v>
       </c>
       <c r="G49" t="n">
-        <v>16.25</v>
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>
@@ -5560,19 +5560,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E4" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>394</v>
+        <v>289</v>
       </c>
       <c r="G4" t="n">
-        <v>146.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="5">
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F9" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="G9" t="n">
-        <v>122.75</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="10">
@@ -5785,19 +5785,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>394</v>
+        <v>289</v>
       </c>
       <c r="G13" t="n">
-        <v>146.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="14">
@@ -5813,16 +5813,16 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F14" t="n">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="G14" t="n">
-        <v>142.75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15">
@@ -5835,19 +5835,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>895</v>
+        <v>510</v>
       </c>
       <c r="G15" t="n">
-        <v>316</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
@@ -5935,19 +5935,19 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" t="n">
         <v>15</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>16</v>
       </c>
-      <c r="E19" t="n">
-        <v>17</v>
-      </c>
-      <c r="F19" t="n">
-        <v>18</v>
-      </c>
       <c r="G19" t="n">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="20">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E23" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F23" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="G23" t="n">
-        <v>122.75</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E24" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="F24" t="n">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="G24" t="n">
-        <v>112.25</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="25">
@@ -6085,19 +6085,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>365</v>
+        <v>167</v>
       </c>
       <c r="F25" t="n">
-        <v>1128</v>
+        <v>478</v>
       </c>
       <c r="G25" t="n">
-        <v>414.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="26">
@@ -6188,16 +6188,16 @@
         <v>21</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="F29" t="n">
-        <v>378</v>
+        <v>309</v>
       </c>
       <c r="G29" t="n">
-        <v>142.75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D30" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>260</v>
+        <v>115</v>
       </c>
       <c r="F30" t="n">
-        <v>895</v>
+        <v>510</v>
       </c>
       <c r="G30" t="n">
-        <v>316</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="F31" t="n">
-        <v>853</v>
+        <v>555</v>
       </c>
       <c r="G31" t="n">
-        <v>268</v>
+        <v>181.75</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D33" t="n">
         <v>24</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F33" t="n">
         <v>24</v>
       </c>
       <c r="G33" t="n">
-        <v>22.25</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="34">
@@ -6360,19 +6360,19 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>18</v>
+      </c>
+      <c r="E36" t="n">
         <v>15</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>16</v>
       </c>
-      <c r="E36" t="n">
-        <v>17</v>
-      </c>
-      <c r="F36" t="n">
-        <v>18</v>
-      </c>
       <c r="G36" t="n">
-        <v>16.5</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="37">
@@ -6385,10 +6385,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
         <v>16</v>
@@ -6397,7 +6397,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D39" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E39" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="F39" t="n">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="G39" t="n">
-        <v>112.25</v>
+        <v>129.75</v>
       </c>
     </row>
     <row r="40">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D40" t="n">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="E40" t="n">
-        <v>365</v>
+        <v>167</v>
       </c>
       <c r="F40" t="n">
-        <v>1128</v>
+        <v>478</v>
       </c>
       <c r="G40" t="n">
-        <v>414.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="41">
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E41" t="n">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="F41" t="n">
-        <v>1077</v>
+        <v>422</v>
       </c>
       <c r="G41" t="n">
-        <v>338.5</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D43" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E43" t="n">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="F43" t="n">
-        <v>853</v>
+        <v>555</v>
       </c>
       <c r="G43" t="n">
-        <v>268</v>
+        <v>181.75</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D44" t="n">
         <v>24</v>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
         <v>24</v>
       </c>
       <c r="G44" t="n">
-        <v>22.25</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="45">
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E45" t="n">
         <v>25</v>
@@ -6597,7 +6597,7 @@
         <v>25</v>
       </c>
       <c r="G45" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="46">
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>16</v>
       </c>
       <c r="G47" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="48">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D48" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E48" t="n">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="F48" t="n">
-        <v>1077</v>
+        <v>422</v>
       </c>
       <c r="G48" t="n">
-        <v>338.5</v>
+        <v>171</v>
       </c>
     </row>
     <row r="49">
@@ -6685,10 +6685,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" t="n">
         <v>25</v>
@@ -6697,7 +6697,7 @@
         <v>25</v>
       </c>
       <c r="G49" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
     </row>
   </sheetData>
@@ -6811,19 +6811,19 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
-        <v>17</v>
-      </c>
       <c r="F4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G4" t="n">
-        <v>14.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -6942,10 +6942,10 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
         <v>8.5</v>
@@ -7036,19 +7036,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -7061,19 +7061,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="15">
@@ -7086,19 +7086,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>12.75</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="16">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -7248,7 +7248,7 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -7286,19 +7286,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -7314,16 +7314,16 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12</v>
-      </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="25">
@@ -7345,10 +7345,10 @@
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -7361,19 +7361,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -7436,19 +7436,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -7486,19 +7486,19 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>9</v>
+      </c>
+      <c r="D31" t="n">
         <v>8</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="n">
-        <v>14</v>
-      </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G31" t="n">
-        <v>10.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="32">
@@ -7542,13 +7542,13 @@
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F33" t="n">
         <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -7586,7 +7586,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -7598,7 +7598,7 @@
         <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -7611,19 +7611,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
@@ -7673,7 +7673,7 @@
         <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -7686,19 +7686,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -7711,19 +7711,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -7742,13 +7742,13 @@
         <v>6</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="42">
@@ -7761,19 +7761,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -7786,19 +7786,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -7811,19 +7811,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -7839,7 +7839,7 @@
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E45" t="n">
         <v>8</v>
@@ -7848,7 +7848,7 @@
         <v>8</v>
       </c>
       <c r="G45" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -7861,19 +7861,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -7886,19 +7886,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -7911,19 +7911,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -7936,19 +7936,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C4" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D4" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E4" t="n">
-        <v>863</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="E9" t="n">
-        <v>801</v>
+        <v>909</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C13" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E13" t="n">
-        <v>863</v>
+        <v>854</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D14" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E14" t="n">
-        <v>836</v>
+        <v>903</v>
       </c>
     </row>
     <row r="15">
@@ -8246,16 +8246,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C15" t="n">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="D15" t="n">
-        <v>540</v>
+        <v>352</v>
       </c>
       <c r="E15" t="n">
-        <v>1489</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="16">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
+        <v>26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22</v>
+      </c>
+      <c r="E19" t="n">
         <v>23</v>
-      </c>
-      <c r="D19" t="n">
-        <v>24</v>
-      </c>
-      <c r="E19" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C23" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D23" t="n">
-        <v>366</v>
+        <v>420</v>
       </c>
       <c r="E23" t="n">
-        <v>801</v>
+        <v>909</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C24" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D24" t="n">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="E24" t="n">
-        <v>734</v>
+        <v>896</v>
       </c>
     </row>
     <row r="25">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C25" t="n">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="D25" t="n">
-        <v>641</v>
+        <v>429</v>
       </c>
       <c r="E25" t="n">
-        <v>1717</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C29" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D29" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E29" t="n">
-        <v>836</v>
+        <v>903</v>
       </c>
     </row>
     <row r="30">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C30" t="n">
-        <v>201</v>
+        <v>146</v>
       </c>
       <c r="D30" t="n">
-        <v>540</v>
+        <v>352</v>
       </c>
       <c r="E30" t="n">
-        <v>1489</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D31" t="n">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="E31" t="n">
-        <v>1458</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="32">
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C33" t="n">
         <v>40</v>
@@ -8597,7 +8597,7 @@
         <v>39</v>
       </c>
       <c r="E33" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -8645,16 +8645,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C36" t="n">
+        <v>26</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E36" t="n">
         <v>23</v>
-      </c>
-      <c r="D36" t="n">
-        <v>24</v>
-      </c>
-      <c r="E36" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="37">
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C37" t="n">
         <v>25</v>
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C39" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D39" t="n">
-        <v>347</v>
+        <v>393</v>
       </c>
       <c r="E39" t="n">
-        <v>734</v>
+        <v>896</v>
       </c>
     </row>
     <row r="40">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C40" t="n">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="D40" t="n">
-        <v>641</v>
+        <v>429</v>
       </c>
       <c r="E40" t="n">
-        <v>1717</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="41">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C41" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D41" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E41" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C43" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D43" t="n">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="E43" t="n">
-        <v>1458</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="44">
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C44" t="n">
         <v>40</v>
@@ -8806,7 +8806,7 @@
         <v>39</v>
       </c>
       <c r="E44" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -8816,7 +8816,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" t="n">
         <v>43</v>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C47" t="n">
         <v>25</v>
@@ -8873,16 +8873,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C48" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D48" t="n">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="E48" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="49">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" t="n">
         <v>43</v>

--- a/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
+++ b/Excel/Validasi/Hasil_Pengujian_Map_4_128_avg_length.xlsx
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0007156</v>
+        <v>0.000717</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0055638</v>
+        <v>0.0055118</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0476005</v>
+        <v>0.0465013</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3275252</v>
+        <v>0.3183174</v>
       </c>
       <c r="G2" t="n">
-        <v>0.095351275</v>
+        <v>0.09276187500000001</v>
       </c>
     </row>
     <row r="3">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0002566</v>
+        <v>0.0002754</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000949</v>
+        <v>0.0013001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0036597</v>
+        <v>0.003583199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0152924</v>
+        <v>0.0160937</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005039425</v>
+        <v>0.005313099999999999</v>
       </c>
     </row>
     <row r="4">
@@ -556,19 +556,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0004205</v>
+        <v>0.0004643000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0010958</v>
+        <v>0.001511</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004232499999999999</v>
+        <v>0.0108756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0183858</v>
+        <v>0.092317</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00603365</v>
+        <v>0.026291975</v>
       </c>
     </row>
     <row r="5">
@@ -581,19 +581,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0005861</v>
+        <v>0.0006058</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0035187</v>
+        <v>0.0034278</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0229887</v>
+        <v>0.0223417</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1579327</v>
+        <v>0.1514367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04625655</v>
+        <v>0.04445299999999999</v>
       </c>
     </row>
     <row r="6">
@@ -606,19 +606,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0006101</v>
+        <v>0.0005839</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0020775</v>
+        <v>0.0020146</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0075617</v>
+        <v>0.007431200000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03146120000000001</v>
+        <v>0.030449</v>
       </c>
       <c r="G6" t="n">
-        <v>0.010427625</v>
+        <v>0.010119675</v>
       </c>
     </row>
     <row r="7">
@@ -631,19 +631,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0007934</v>
+        <v>0.0008386999999999998</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0056369</v>
+        <v>0.0055471</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04769320000000001</v>
+        <v>0.04703710000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3320585</v>
+        <v>0.3183032</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09654549999999999</v>
+        <v>0.092931525</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0009327000000000001</v>
+        <v>0.0009842</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0067103</v>
+        <v>0.0066566</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04839880000000001</v>
+        <v>0.0461819</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3265101</v>
+        <v>0.3156759000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09563797499999999</v>
+        <v>0.09237465000000002</v>
       </c>
     </row>
     <row r="9">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0004056</v>
+        <v>0.0003663000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0010508</v>
+        <v>0.0008273000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0026066</v>
+        <v>0.002764399999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007560800000000001</v>
+        <v>0.0136618</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00290595</v>
+        <v>0.00440495</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003405</v>
+        <v>0.0003234</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0012473</v>
+        <v>0.0012366</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0051008</v>
+        <v>0.0050331</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0211359</v>
+        <v>0.0202769</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006956125000000001</v>
+        <v>0.0067175</v>
       </c>
     </row>
     <row r="11">
@@ -731,19 +731,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0002846</v>
+        <v>0.0002815</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0010389</v>
+        <v>0.0015032</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0039076</v>
+        <v>0.003860999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0164304</v>
+        <v>0.0159669</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005415375</v>
+        <v>0.00540315</v>
       </c>
     </row>
     <row r="12">
@@ -756,19 +756,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003301000000000001</v>
+        <v>0.0003376</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0010739</v>
+        <v>0.0013254</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004059200000000001</v>
+        <v>0.0040726</v>
       </c>
       <c r="F12" t="n">
-        <v>0.015643</v>
+        <v>0.0153499</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005276550000000001</v>
+        <v>0.005271375</v>
       </c>
     </row>
     <row r="13">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004326999999999999</v>
+        <v>0.0004411</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0011746</v>
+        <v>0.0015713</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0045699</v>
+        <v>0.0110479</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0195259</v>
+        <v>0.0916797</v>
       </c>
       <c r="G13" t="n">
-        <v>0.006425775000000001</v>
+        <v>0.026185</v>
       </c>
     </row>
     <row r="14">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004272</v>
+        <v>0.0004558</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0011982</v>
+        <v>0.0015612</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0043693</v>
+        <v>0.0110306</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0203732</v>
+        <v>0.09323000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.006591975</v>
+        <v>0.0265694</v>
       </c>
     </row>
     <row r="15">
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0005328</v>
+        <v>0.0005723000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0013076</v>
+        <v>0.00345</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0044917</v>
+        <v>0.0135933</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0327703</v>
+        <v>0.1144552</v>
       </c>
       <c r="G15" t="n">
-        <v>0.009775600000000001</v>
+        <v>0.0330177</v>
       </c>
     </row>
     <row r="16">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0006322000000000001</v>
+        <v>0.0006310000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0036029</v>
+        <v>0.0035375</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0235995</v>
+        <v>0.0225213</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1580801</v>
+        <v>0.1519205</v>
       </c>
       <c r="G16" t="n">
-        <v>0.046478675</v>
+        <v>0.044652575</v>
       </c>
     </row>
     <row r="17">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0005668</v>
+        <v>0.000581</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0030473</v>
+        <v>0.0030973</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0195492</v>
+        <v>0.0186956</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1488626</v>
+        <v>0.1407053</v>
       </c>
       <c r="G17" t="n">
-        <v>0.043006475</v>
+        <v>0.04076979999999999</v>
       </c>
     </row>
     <row r="18">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003853</v>
+        <v>0.0003885000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0015601</v>
+        <v>0.0016322</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0057353</v>
+        <v>0.0058359</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0224186</v>
+        <v>0.0218268</v>
       </c>
       <c r="G18" t="n">
-        <v>0.007524825000000001</v>
+        <v>0.00742085</v>
       </c>
     </row>
     <row r="19">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002904</v>
+        <v>0.000316</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0011592</v>
+        <v>0.0008423</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0034086</v>
+        <v>0.0030263</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0131264</v>
+        <v>0.011769</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004496150000000001</v>
+        <v>0.0039884</v>
       </c>
     </row>
     <row r="20">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0005181000000000001</v>
+        <v>0.0004882</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0017371</v>
+        <v>0.0017818</v>
       </c>
       <c r="E20" t="n">
-        <v>0.006408899999999999</v>
+        <v>0.0060725</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0241837</v>
+        <v>0.0232727</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008211949999999999</v>
+        <v>0.007903799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -981,19 +981,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0006422000000000001</v>
+        <v>0.0006108000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0021</v>
+        <v>0.0020876</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0076461</v>
+        <v>0.0074573</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0317962</v>
+        <v>0.0305511</v>
       </c>
       <c r="G21" t="n">
-        <v>0.010546125</v>
+        <v>0.0101767</v>
       </c>
     </row>
     <row r="22">
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001004</v>
+        <v>0.0009921999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.007885</v>
+        <v>0.0067641</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0490782</v>
+        <v>0.046809</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3309083</v>
+        <v>0.3156177</v>
       </c>
       <c r="G22" t="n">
-        <v>0.097218875</v>
+        <v>0.09254575</v>
       </c>
     </row>
     <row r="23">
@@ -1031,19 +1031,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004478</v>
+        <v>0.0003746</v>
       </c>
       <c r="D23" t="n">
-        <v>0.001113</v>
+        <v>0.0008974999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0028218</v>
+        <v>0.002981</v>
       </c>
       <c r="F23" t="n">
-        <v>0.008396400000000002</v>
+        <v>0.0143682</v>
       </c>
       <c r="G23" t="n">
-        <v>0.003194750000000001</v>
+        <v>0.004655325</v>
       </c>
     </row>
     <row r="24">
@@ -1056,19 +1056,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004641</v>
+        <v>0.0003848</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0011287</v>
+        <v>0.0009151</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0028351</v>
+        <v>0.0028792</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0081403</v>
+        <v>0.0139206</v>
       </c>
       <c r="G24" t="n">
-        <v>0.00314205</v>
+        <v>0.004524925</v>
       </c>
     </row>
     <row r="25">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0005700999999999999</v>
+        <v>0.0005222</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00114</v>
+        <v>0.0016065</v>
       </c>
       <c r="E25" t="n">
-        <v>0.003362900000000001</v>
+        <v>0.0051617</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0138207</v>
+        <v>0.0265618</v>
       </c>
       <c r="G25" t="n">
-        <v>0.004723425</v>
+        <v>0.00846305</v>
       </c>
     </row>
     <row r="26">
@@ -1106,19 +1106,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003511</v>
+        <v>0.0003575</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0013239</v>
+        <v>0.0013471</v>
       </c>
       <c r="E26" t="n">
-        <v>0.005453700000000001</v>
+        <v>0.005166700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0222523</v>
+        <v>0.0212714</v>
       </c>
       <c r="G26" t="n">
-        <v>0.00734525</v>
+        <v>0.007035675000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1134,16 +1134,16 @@
         <v>0.0003752</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0014419</v>
+        <v>0.0014231</v>
       </c>
       <c r="E27" t="n">
-        <v>0.005398999999999999</v>
+        <v>0.005209899999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0218032</v>
+        <v>0.0212901</v>
       </c>
       <c r="G27" t="n">
-        <v>0.007254825</v>
+        <v>0.007074575</v>
       </c>
     </row>
     <row r="28">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003599000000000001</v>
+        <v>0.0003505</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0011633</v>
+        <v>0.001161</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0044339</v>
+        <v>0.0043513</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01711</v>
+        <v>0.016584</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005766774999999999</v>
+        <v>0.005611700000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0004694</v>
+        <v>0.0005172</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0012645</v>
+        <v>0.0016297</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0046141</v>
+        <v>0.0109452</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0213946</v>
+        <v>0.0930465</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006935650000000001</v>
+        <v>0.02653465</v>
       </c>
     </row>
     <row r="30">
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0005954000000000001</v>
+        <v>0.0005923</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0013362</v>
+        <v>0.0035786</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0047093</v>
+        <v>0.013563</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03408899999999999</v>
+        <v>0.1152609</v>
       </c>
       <c r="G30" t="n">
-        <v>0.010182475</v>
+        <v>0.03324869999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1231,19 +1231,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0006293000000000001</v>
+        <v>0.0005781</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00129</v>
+        <v>0.0038016</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0042204</v>
+        <v>0.009516</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0360269</v>
+        <v>0.0881575</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01054165</v>
+        <v>0.0255133</v>
       </c>
     </row>
     <row r="32">
@@ -1256,19 +1256,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000607</v>
+        <v>0.0006163</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0031782</v>
+        <v>0.0031393</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0195168</v>
+        <v>0.0193765</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1492431</v>
+        <v>0.1424622</v>
       </c>
       <c r="G32" t="n">
-        <v>0.043136275</v>
+        <v>0.04139857499999999</v>
       </c>
     </row>
     <row r="33">
@@ -1281,19 +1281,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0003457999999999999</v>
+        <v>0.0003129</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0019938</v>
+        <v>0.0014543</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006326099999999999</v>
+        <v>0.005536399999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0258252</v>
+        <v>0.0166523</v>
       </c>
       <c r="G33" t="n">
-        <v>0.008622724999999999</v>
+        <v>0.005988975000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1306,19 +1306,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0004891</v>
+        <v>0.0004536</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0020816</v>
+        <v>0.0019001</v>
       </c>
       <c r="E34" t="n">
-        <v>0.006866300000000001</v>
+        <v>0.0067366</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0268445</v>
+        <v>0.0262064</v>
       </c>
       <c r="G34" t="n">
-        <v>0.009070375</v>
+        <v>0.008824175</v>
       </c>
     </row>
     <row r="35">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0004442999999999999</v>
+        <v>0.0004037</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0016444</v>
+        <v>0.0015954</v>
       </c>
       <c r="E35" t="n">
-        <v>0.005908200000000001</v>
+        <v>0.0059018</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02281</v>
+        <v>0.0220588</v>
       </c>
       <c r="G35" t="n">
-        <v>0.007701725</v>
+        <v>0.007489925</v>
       </c>
     </row>
     <row r="36">
@@ -1356,19 +1356,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.000339</v>
+        <v>0.000297</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0011946</v>
+        <v>0.0009100999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0034093</v>
+        <v>0.0031211</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0131543</v>
+        <v>0.0118384</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0045243</v>
+        <v>0.004041650000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0003591000000000001</v>
+        <v>0.0003525000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0010907</v>
+        <v>0.0013935</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0035996</v>
+        <v>0.004066700000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0136828</v>
+        <v>0.0153272</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00468305</v>
+        <v>0.005284975</v>
       </c>
     </row>
     <row r="38">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0005572999999999999</v>
+        <v>0.0005429</v>
       </c>
       <c r="D38" t="n">
-        <v>0.001806</v>
+        <v>0.0019157</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0062168</v>
+        <v>0.0061598</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0244056</v>
+        <v>0.0234836</v>
       </c>
       <c r="G38" t="n">
-        <v>0.008246425</v>
+        <v>0.0080255</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0004466</v>
+        <v>0.0004348000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0012492</v>
+        <v>0.0009793000000000002</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0030373</v>
+        <v>0.0030311</v>
       </c>
       <c r="F39" t="n">
-        <v>0.009071300000000001</v>
+        <v>0.0145399</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0034511</v>
+        <v>0.004746274999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1456,19 +1456,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0006461999999999999</v>
+        <v>0.0005399</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0012489</v>
+        <v>0.0017267</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0036216</v>
+        <v>0.005464800000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0145101</v>
+        <v>0.0274894</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0050067</v>
+        <v>0.008805200000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1481,19 +1481,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0006454000000000001</v>
+        <v>0.0005646</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0012132</v>
+        <v>0.0016837</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0036287</v>
+        <v>0.0047456</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0120211</v>
+        <v>0.0254609</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0043771</v>
+        <v>0.0081137</v>
       </c>
     </row>
     <row r="42">
@@ -1506,19 +1506,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0004918</v>
+        <v>0.0003938</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0014965</v>
+        <v>0.0015121</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0057905</v>
+        <v>0.0056103</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0230931</v>
+        <v>0.0222121</v>
       </c>
       <c r="G42" t="n">
-        <v>0.007717975</v>
+        <v>0.007432075000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1531,19 +1531,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0006453</v>
+        <v>0.0006528</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0013504</v>
+        <v>0.0039142</v>
       </c>
       <c r="E43" t="n">
-        <v>0.004421</v>
+        <v>0.009707499999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0369717</v>
+        <v>0.08900379999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0108471</v>
+        <v>0.025819575</v>
       </c>
     </row>
     <row r="44">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0003664</v>
+        <v>0.000306</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0019892</v>
+        <v>0.0015465</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006336800000000001</v>
+        <v>0.0053931</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0257075</v>
+        <v>0.0167728</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008599975000000001</v>
+        <v>0.006004600000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004005</v>
+        <v>0.0003396000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0.001986299999999999</v>
+        <v>0.0011366</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0068523</v>
+        <v>0.004143</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0248899</v>
+        <v>0.0153197</v>
       </c>
       <c r="G45" t="n">
-        <v>0.00853225</v>
+        <v>0.005234725</v>
       </c>
     </row>
     <row r="46">
@@ -1606,19 +1606,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0004878</v>
+        <v>0.0004754000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0020998</v>
+        <v>0.0019303</v>
       </c>
       <c r="E46" t="n">
-        <v>0.006909800000000001</v>
+        <v>0.006973999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0266316</v>
+        <v>0.0260942</v>
       </c>
       <c r="G46" t="n">
-        <v>0.009032249999999999</v>
+        <v>0.008868475000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1631,19 +1631,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0003775</v>
+        <v>0.0003656</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0011277</v>
+        <v>0.0014164</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0037401</v>
+        <v>0.0041368</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0138309</v>
+        <v>0.015233</v>
       </c>
       <c r="G47" t="n">
-        <v>0.00476905</v>
+        <v>0.00528795</v>
       </c>
     </row>
     <row r="48">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0007030999999999999</v>
+        <v>0.0006241</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0013255</v>
+        <v>0.0018455</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0035712</v>
+        <v>0.0050559</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0130827</v>
+        <v>0.0263763</v>
       </c>
       <c r="G48" t="n">
-        <v>0.004670624999999999</v>
+        <v>0.008475450000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004228000000000001</v>
+        <v>0.0003718</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0020322</v>
+        <v>0.0012318</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0066852</v>
+        <v>0.0042644</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0254287</v>
+        <v>0.0153965</v>
       </c>
       <c r="G49" t="n">
-        <v>0.008642225</v>
+        <v>0.005316125</v>
       </c>
     </row>
   </sheetData>
@@ -1813,13 +1813,13 @@
         <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="G4" t="n">
-        <v>81.75</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="5">
@@ -1941,10 +1941,10 @@
         <v>80</v>
       </c>
       <c r="F9" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="10">
@@ -2032,19 +2032,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -2063,13 +2063,13 @@
         <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="G14" t="n">
-        <v>81.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
@@ -2085,16 +2085,16 @@
         <v>21</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
         <v>84</v>
       </c>
       <c r="F15" t="n">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="G15" t="n">
-        <v>82.75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -2185,16 +2185,16 @@
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>14.25</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="20">
@@ -2316,10 +2316,10 @@
         <v>80</v>
       </c>
       <c r="F24" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G24" t="n">
-        <v>75</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="25">
@@ -2332,19 +2332,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G25" t="n">
-        <v>78.25</v>
+        <v>77.75</v>
       </c>
     </row>
     <row r="26">
@@ -2432,19 +2432,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -2460,7 +2460,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
         <v>6</v>
@@ -2469,7 +2469,7 @@
         <v>6</v>
       </c>
       <c r="G30" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="31">
@@ -2485,16 +2485,16 @@
         <v>21</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E31" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F31" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G31" t="n">
-        <v>77.25</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="32">
@@ -2538,13 +2538,13 @@
         <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
         <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="34">
@@ -2610,16 +2610,16 @@
         <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D37" t="n">
         <v>15</v>
@@ -2644,7 +2644,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="n">
-        <v>14.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="38">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
         <v>6</v>
@@ -2719,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="G40" t="n">
-        <v>5.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="41">
@@ -2732,7 +2732,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D41" t="n">
         <v>40</v>
@@ -2744,7 +2744,7 @@
         <v>160</v>
       </c>
       <c r="G41" t="n">
-        <v>75.25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
@@ -2785,7 +2785,7 @@
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="n">
         <v>6</v>
@@ -2794,7 +2794,7 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="44">
@@ -2810,16 +2810,16 @@
         <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="45">
@@ -2832,19 +2832,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G45" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="46">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
         <v>5</v>
@@ -2894,7 +2894,7 @@
         <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
         <v>6</v>
@@ -2919,7 +2919,7 @@
         <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -2932,19 +2932,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.55634918610405</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D4" t="n">
-        <v>48.52691193458118</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E4" t="n">
-        <v>103.7401153701776</v>
+        <v>100.1248916810278</v>
       </c>
       <c r="F4" t="n">
-        <v>208.8944443027283</v>
+        <v>202.2497833620557</v>
       </c>
       <c r="G4" t="n">
-        <v>96.17945519839779</v>
+        <v>94.02869760331529</v>
       </c>
     </row>
     <row r="5">
@@ -3189,13 +3189,13 @@
         <v>48.52691193458118</v>
       </c>
       <c r="E9" t="n">
-        <v>99.29646455628166</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F9" t="n">
-        <v>199.1787155501902</v>
+        <v>198.9360748630709</v>
       </c>
       <c r="G9" t="n">
-        <v>92.63961030678928</v>
+        <v>92.3718433538229</v>
       </c>
     </row>
     <row r="10">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.52857279783051</v>
+        <v>23.67219397135701</v>
       </c>
       <c r="D13" t="n">
-        <v>46.26086081946685</v>
+        <v>47.67823847813622</v>
       </c>
       <c r="E13" t="n">
-        <v>95.97749958777082</v>
+        <v>97.05168647377276</v>
       </c>
       <c r="F13" t="n">
-        <v>193.9074207545753</v>
+        <v>195.7096081964235</v>
       </c>
       <c r="G13" t="n">
-        <v>89.66858848991086</v>
+        <v>91.02793177992237</v>
       </c>
     </row>
     <row r="14">
@@ -3308,19 +3308,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.55634918610405</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D14" t="n">
-        <v>48.52691193458118</v>
+        <v>49.35533905932738</v>
       </c>
       <c r="E14" t="n">
-        <v>103.1543289325507</v>
+        <v>100.1248916810278</v>
       </c>
       <c r="F14" t="n">
-        <v>208.8944443027283</v>
+        <v>202.492424049175</v>
       </c>
       <c r="G14" t="n">
-        <v>96.03300858899107</v>
+        <v>94.08935777509511</v>
       </c>
     </row>
     <row r="15">
@@ -3336,16 +3336,16 @@
         <v>24.97056274847714</v>
       </c>
       <c r="D15" t="n">
-        <v>49.1126983722081</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="E15" t="n">
         <v>100.8111831820431</v>
       </c>
       <c r="F15" t="n">
-        <v>215.4802307403552</v>
+        <v>203.6223663640862</v>
       </c>
       <c r="G15" t="n">
-        <v>97.5936687607709</v>
+        <v>94.98275605729691</v>
       </c>
     </row>
     <row r="16">
@@ -3436,16 +3436,16 @@
         <v>23.55634918610405</v>
       </c>
       <c r="D19" t="n">
-        <v>49.69848480983499</v>
+        <v>48.52691193458118</v>
       </c>
       <c r="E19" t="n">
-        <v>100.8111831820431</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F19" t="n">
-        <v>203.0365799264593</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G19" t="n">
-        <v>94.27564927611036</v>
+        <v>92.22539674441617</v>
       </c>
     </row>
     <row r="20">
@@ -3564,13 +3564,13 @@
         <v>48.52691193458118</v>
       </c>
       <c r="E24" t="n">
-        <v>99.29646455628166</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F24" t="n">
-        <v>198.350288425444</v>
+        <v>200.350288425444</v>
       </c>
       <c r="G24" t="n">
-        <v>92.43250352560273</v>
+        <v>92.72539674441617</v>
       </c>
     </row>
     <row r="25">
@@ -3583,19 +3583,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.97056274847714</v>
+        <v>27.79898987322333</v>
       </c>
       <c r="D25" t="n">
-        <v>49.94112549695429</v>
+        <v>54.52691193458119</v>
       </c>
       <c r="E25" t="n">
-        <v>100.2253967444162</v>
+        <v>99.05382386916236</v>
       </c>
       <c r="F25" t="n">
-        <v>203.8650070512055</v>
+        <v>198.9360748630709</v>
       </c>
       <c r="G25" t="n">
-        <v>94.75052301026329</v>
+        <v>95.07895013500945</v>
       </c>
     </row>
     <row r="26">
@@ -3683,19 +3683,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22.52857279783051</v>
+        <v>23.67219397135701</v>
       </c>
       <c r="D29" t="n">
-        <v>46.26086081946685</v>
+        <v>47.67823847813622</v>
       </c>
       <c r="E29" t="n">
-        <v>95.97749958777082</v>
+        <v>97.05168647377276</v>
       </c>
       <c r="F29" t="n">
-        <v>193.9074207545753</v>
+        <v>194.5453197737502</v>
       </c>
       <c r="G29" t="n">
-        <v>89.66858848991086</v>
+        <v>90.73685967425403</v>
       </c>
     </row>
     <row r="30">
@@ -3711,16 +3711,16 @@
         <v>22.85730076213408</v>
       </c>
       <c r="D30" t="n">
-        <v>46.26086081946685</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E30" t="n">
-        <v>93.8728585920724</v>
+        <v>93.75984369729352</v>
       </c>
       <c r="F30" t="n">
-        <v>192.1148020630235</v>
+        <v>188.7720118080779</v>
       </c>
       <c r="G30" t="n">
-        <v>88.77645555917422</v>
+        <v>88.02215430017574</v>
       </c>
     </row>
     <row r="31">
@@ -3736,16 +3736,16 @@
         <v>24.97056274847714</v>
       </c>
       <c r="D31" t="n">
-        <v>48.52691193458118</v>
+        <v>50.52691193458118</v>
       </c>
       <c r="E31" t="n">
-        <v>99.05382386916236</v>
+        <v>98.46803743153546</v>
       </c>
       <c r="F31" t="n">
-        <v>202.4507934888324</v>
+        <v>198.350288425444</v>
       </c>
       <c r="G31" t="n">
-        <v>93.75052301026327</v>
+        <v>93.07895013500945</v>
       </c>
     </row>
     <row r="32">
@@ -3783,19 +3783,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25.31370849898476</v>
+        <v>23.55634918610405</v>
       </c>
       <c r="D33" t="n">
-        <v>49.69848480983499</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E33" t="n">
-        <v>100.8111831820431</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="F33" t="n">
-        <v>203.0365799264593</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G33" t="n">
-        <v>94.71498910433053</v>
+        <v>98.3761543394987</v>
       </c>
     </row>
     <row r="34">
@@ -3861,16 +3861,16 @@
         <v>22.84376684661083</v>
       </c>
       <c r="D36" t="n">
-        <v>46.69946093319749</v>
+        <v>47.10174725559475</v>
       </c>
       <c r="E36" t="n">
-        <v>94.48572750867693</v>
+        <v>95.61770807356257</v>
       </c>
       <c r="F36" t="n">
-        <v>190.0974453381104</v>
+        <v>192.6496297094982</v>
       </c>
       <c r="G36" t="n">
-        <v>88.53160015664891</v>
+        <v>89.5532129713166</v>
       </c>
     </row>
     <row r="37">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>23.55634918610405</v>
+        <v>24.14213562373095</v>
       </c>
       <c r="D37" t="n">
         <v>49.69848480983499</v>
@@ -3895,7 +3895,7 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G37" t="n">
-        <v>94.27564927611036</v>
+        <v>94.42209588551708</v>
       </c>
     </row>
     <row r="38">
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>22.84376684661083</v>
+        <v>22.52857279783051</v>
       </c>
       <c r="D39" t="n">
         <v>46.26086081946685</v>
@@ -3945,7 +3945,7 @@
         <v>188.7720118080779</v>
       </c>
       <c r="G39" t="n">
-        <v>87.90912079286227</v>
+        <v>87.83032228066719</v>
       </c>
     </row>
     <row r="40">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22.85730076213408</v>
+        <v>24.64222328045784</v>
       </c>
       <c r="D40" t="n">
-        <v>46.26086081946685</v>
+        <v>49.98369828040286</v>
       </c>
       <c r="E40" t="n">
         <v>93.75984369729352</v>
@@ -3970,7 +3970,7 @@
         <v>188.7720118080779</v>
       </c>
       <c r="G40" t="n">
-        <v>87.91250427174307</v>
+        <v>89.28944426655802</v>
       </c>
     </row>
     <row r="41">
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>24.97056274847714</v>
+        <v>24.38477631085024</v>
       </c>
       <c r="D41" t="n">
         <v>48.52691193458118</v>
@@ -3995,7 +3995,7 @@
         <v>198.350288425444</v>
       </c>
       <c r="G41" t="n">
-        <v>92.57895013500945</v>
+        <v>92.43250352560273</v>
       </c>
     </row>
     <row r="42">
@@ -4036,16 +4036,16 @@
         <v>22.99699583160862</v>
       </c>
       <c r="D43" t="n">
-        <v>46.26086081946685</v>
+        <v>46.69946093319749</v>
       </c>
       <c r="E43" t="n">
-        <v>93.8728585920724</v>
+        <v>95.23288087711589</v>
       </c>
       <c r="F43" t="n">
-        <v>189.9438919833272</v>
+        <v>192.2505641855635</v>
       </c>
       <c r="G43" t="n">
-        <v>88.26865180661878</v>
+        <v>89.29497545687138</v>
       </c>
     </row>
     <row r="44">
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23.80590802780531</v>
+        <v>22.63292806537241</v>
       </c>
       <c r="D44" t="n">
-        <v>47.62902808688504</v>
+        <v>49.24403941122092</v>
       </c>
       <c r="E44" t="n">
-        <v>94.48572750867693</v>
+        <v>99.26201990681295</v>
       </c>
       <c r="F44" t="n">
-        <v>193.604162987165</v>
+        <v>199.3577857159867</v>
       </c>
       <c r="G44" t="n">
-        <v>89.88120665263305</v>
+        <v>92.62419327484824</v>
       </c>
     </row>
     <row r="45">
@@ -4086,16 +4086,16 @@
         <v>25.31370849898476</v>
       </c>
       <c r="D45" t="n">
-        <v>49.69848480983499</v>
+        <v>52.04163056034262</v>
       </c>
       <c r="E45" t="n">
-        <v>100.8111831820431</v>
+        <v>105.4974746830583</v>
       </c>
       <c r="F45" t="n">
-        <v>203.0365799264593</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G45" t="n">
-        <v>94.71498910433053</v>
+        <v>98.81549416771887</v>
       </c>
     </row>
     <row r="46">
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22.84376684661083</v>
+        <v>22.85730076213408</v>
       </c>
       <c r="D47" t="n">
         <v>46.69946093319749</v>
@@ -4145,7 +4145,7 @@
         <v>190.0974453381104</v>
       </c>
       <c r="G47" t="n">
-        <v>88.53160015664891</v>
+        <v>88.53498363552973</v>
       </c>
     </row>
     <row r="48">
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>22.85730076213408</v>
+        <v>22.52857279783051</v>
       </c>
       <c r="D48" t="n">
         <v>46.26086081946685</v>
@@ -4170,7 +4170,7 @@
         <v>188.7720118080779</v>
       </c>
       <c r="G48" t="n">
-        <v>87.91250427174307</v>
+        <v>87.83032228066719</v>
       </c>
     </row>
     <row r="49">
@@ -4183,19 +4183,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>23.80590802780531</v>
+        <v>24.31077224838296</v>
       </c>
       <c r="D49" t="n">
-        <v>46.69946093319749</v>
+        <v>49.24403941122092</v>
       </c>
       <c r="E49" t="n">
-        <v>94.48572750867693</v>
+        <v>99.26201990681295</v>
       </c>
       <c r="F49" t="n">
-        <v>190.0974453381104</v>
+        <v>199.3577857159867</v>
       </c>
       <c r="G49" t="n">
-        <v>88.77213545194753</v>
+        <v>93.04365432060089</v>
       </c>
     </row>
   </sheetData>
@@ -4309,19 +4309,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E4" t="n">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="F4" t="n">
-        <v>565</v>
+        <v>614</v>
       </c>
       <c r="G4" t="n">
-        <v>236.25</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5">
@@ -4434,19 +4434,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E9" t="n">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="F9" t="n">
-        <v>616</v>
+        <v>523</v>
       </c>
       <c r="G9" t="n">
-        <v>265</v>
+        <v>221.25</v>
       </c>
     </row>
     <row r="10">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E13" t="n">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="F13" t="n">
-        <v>565</v>
+        <v>614</v>
       </c>
       <c r="G13" t="n">
-        <v>236.25</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
       </c>
       <c r="E14" t="n">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="F14" t="n">
-        <v>594</v>
+        <v>633</v>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="15">
@@ -4584,19 +4584,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="F15" t="n">
-        <v>567</v>
+        <v>729</v>
       </c>
       <c r="G15" t="n">
-        <v>237.5</v>
+        <v>295.25</v>
       </c>
     </row>
     <row r="16">
@@ -4690,13 +4690,13 @@
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="20">
@@ -4784,19 +4784,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="E23" t="n">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="F23" t="n">
-        <v>616</v>
+        <v>523</v>
       </c>
       <c r="G23" t="n">
-        <v>265</v>
+        <v>221.25</v>
       </c>
     </row>
     <row r="24">
@@ -4809,19 +4809,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D24" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E24" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="F24" t="n">
-        <v>606</v>
+        <v>521</v>
       </c>
       <c r="G24" t="n">
-        <v>255.5</v>
+        <v>219.75</v>
       </c>
     </row>
     <row r="25">
@@ -4834,19 +4834,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D25" t="n">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="E25" t="n">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="F25" t="n">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="G25" t="n">
-        <v>261.75</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26">
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" t="n">
         <v>103</v>
       </c>
       <c r="E29" t="n">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="F29" t="n">
-        <v>594</v>
+        <v>633</v>
       </c>
       <c r="G29" t="n">
-        <v>245</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="30">
@@ -4959,19 +4959,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D30" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E30" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="F30" t="n">
-        <v>567</v>
+        <v>729</v>
       </c>
       <c r="G30" t="n">
-        <v>237.5</v>
+        <v>295.25</v>
       </c>
     </row>
     <row r="31">
@@ -4984,19 +4984,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E31" t="n">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="F31" t="n">
-        <v>556</v>
+        <v>716</v>
       </c>
       <c r="G31" t="n">
-        <v>233</v>
+        <v>299.5</v>
       </c>
     </row>
     <row r="32">
@@ -5034,19 +5034,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F33" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -5115,13 +5115,13 @@
         <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="37">
@@ -5134,19 +5134,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="38">
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D39" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E39" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="F39" t="n">
-        <v>606</v>
+        <v>521</v>
       </c>
       <c r="G39" t="n">
-        <v>255.5</v>
+        <v>219.75</v>
       </c>
     </row>
     <row r="40">
@@ -5209,19 +5209,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D40" t="n">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="E40" t="n">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="F40" t="n">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="G40" t="n">
-        <v>261.75</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41">
@@ -5234,19 +5234,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D41" t="n">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E41" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F41" t="n">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="G41" t="n">
-        <v>267.5</v>
+        <v>278.5</v>
       </c>
     </row>
     <row r="42">
@@ -5284,19 +5284,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E43" t="n">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="F43" t="n">
-        <v>556</v>
+        <v>716</v>
       </c>
       <c r="G43" t="n">
-        <v>233</v>
+        <v>299.5</v>
       </c>
     </row>
     <row r="44">
@@ -5309,19 +5309,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -5334,19 +5334,19 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="n">
         <v>12</v>
       </c>
-      <c r="D45" t="n">
-        <v>18</v>
-      </c>
       <c r="E45" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F45" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="46">
@@ -5384,19 +5384,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="48">
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D48" t="n">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E48" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F48" t="n">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="G48" t="n">
-        <v>267.5</v>
+        <v>278.5</v>
       </c>
     </row>
     <row r="49">
@@ -5434,19 +5434,19 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="n">
         <v>12</v>
       </c>
-      <c r="D49" t="n">
-        <v>18</v>
-      </c>
       <c r="E49" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -5563,16 +5563,16 @@
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="F4" t="n">
-        <v>289</v>
+        <v>1176</v>
       </c>
       <c r="G4" t="n">
-        <v>115.5</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="5">
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="F9" t="n">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="G9" t="n">
-        <v>131.5</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="10">
@@ -5788,16 +5788,16 @@
         <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="F13" t="n">
-        <v>289</v>
+        <v>1176</v>
       </c>
       <c r="G13" t="n">
-        <v>115.5</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="14">
@@ -5813,16 +5813,16 @@
         <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="F14" t="n">
-        <v>309</v>
+        <v>1177</v>
       </c>
       <c r="G14" t="n">
-        <v>120</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15">
@@ -5835,19 +5835,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="E15" t="n">
-        <v>115</v>
+        <v>311</v>
       </c>
       <c r="F15" t="n">
-        <v>510</v>
+        <v>1499</v>
       </c>
       <c r="G15" t="n">
-        <v>174</v>
+        <v>486.25</v>
       </c>
     </row>
     <row r="16">
@@ -5938,16 +5938,16 @@
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>15.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="20">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="F23" t="n">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="G23" t="n">
-        <v>131.5</v>
+        <v>124.25</v>
       </c>
     </row>
     <row r="24">
@@ -6060,19 +6060,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="G24" t="n">
-        <v>129.75</v>
+        <v>121.75</v>
       </c>
     </row>
     <row r="25">
@@ -6085,19 +6085,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E25" t="n">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="F25" t="n">
-        <v>478</v>
+        <v>618</v>
       </c>
       <c r="G25" t="n">
-        <v>187.5</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26">
@@ -6188,16 +6188,16 @@
         <v>21</v>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="F29" t="n">
-        <v>309</v>
+        <v>1177</v>
       </c>
       <c r="G29" t="n">
-        <v>120</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30">
@@ -6210,19 +6210,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="E30" t="n">
-        <v>115</v>
+        <v>311</v>
       </c>
       <c r="F30" t="n">
-        <v>510</v>
+        <v>1499</v>
       </c>
       <c r="G30" t="n">
-        <v>174</v>
+        <v>486.25</v>
       </c>
     </row>
     <row r="31">
@@ -6235,19 +6235,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E31" t="n">
-        <v>102</v>
+        <v>232</v>
       </c>
       <c r="F31" t="n">
-        <v>555</v>
+        <v>1191</v>
       </c>
       <c r="G31" t="n">
-        <v>181.75</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32">
@@ -6285,19 +6285,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>21.25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -6363,16 +6363,16 @@
         <v>12</v>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G36" t="n">
-        <v>15.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="37">
@@ -6388,16 +6388,16 @@
         <v>14</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E37" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F37" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
@@ -6435,19 +6435,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D39" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="F39" t="n">
-        <v>290</v>
+        <v>332</v>
       </c>
       <c r="G39" t="n">
-        <v>129.75</v>
+        <v>121.75</v>
       </c>
     </row>
     <row r="40">
@@ -6460,19 +6460,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D40" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E40" t="n">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="F40" t="n">
-        <v>478</v>
+        <v>618</v>
       </c>
       <c r="G40" t="n">
-        <v>187.5</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41">
@@ -6485,19 +6485,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E41" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F41" t="n">
-        <v>422</v>
+        <v>596</v>
       </c>
       <c r="G41" t="n">
-        <v>171</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="42">
@@ -6535,19 +6535,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E43" t="n">
-        <v>102</v>
+        <v>232</v>
       </c>
       <c r="F43" t="n">
-        <v>555</v>
+        <v>1191</v>
       </c>
       <c r="G43" t="n">
-        <v>181.75</v>
+        <v>389</v>
       </c>
     </row>
     <row r="44">
@@ -6560,19 +6560,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E44" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G44" t="n">
-        <v>21.25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45">
@@ -6585,19 +6585,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G45" t="n">
-        <v>22.5</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="46">
@@ -6638,16 +6638,16 @@
         <v>14</v>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F47" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48">
@@ -6660,19 +6660,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D48" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E48" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F48" t="n">
-        <v>422</v>
+        <v>596</v>
       </c>
       <c r="G48" t="n">
-        <v>171</v>
+        <v>217.25</v>
       </c>
     </row>
     <row r="49">
@@ -6685,19 +6685,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G49" t="n">
-        <v>22.5</v>
+        <v>16.25</v>
       </c>
     </row>
   </sheetData>
@@ -6811,19 +6811,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="5">
@@ -6942,13 +6942,13 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -7036,19 +7036,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7061,19 +7061,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="15">
@@ -7092,13 +7092,13 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>14.25</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="16">
@@ -7189,16 +7189,16 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -7317,13 +7317,13 @@
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -7336,19 +7336,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="26">
@@ -7436,19 +7436,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -7489,16 +7489,16 @@
         <v>9</v>
       </c>
       <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" t="n">
         <v>8</v>
       </c>
-      <c r="E31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F31" t="n">
-        <v>12</v>
-      </c>
       <c r="G31" t="n">
-        <v>9.75</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="32">
@@ -7536,19 +7536,19 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
         <v>8</v>
-      </c>
-      <c r="D33" t="n">
-        <v>6</v>
       </c>
       <c r="E33" t="n">
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34">
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
         <v>7</v>
@@ -7648,7 +7648,7 @@
         <v>7</v>
       </c>
       <c r="G37" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -7711,10 +7711,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
@@ -7723,7 +7723,7 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="41">
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
         <v>6</v>
@@ -7745,10 +7745,10 @@
         <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -7811,19 +7811,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="45">
@@ -7936,19 +7936,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8037,16 +8037,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D4" t="n">
-        <v>347</v>
+        <v>555</v>
       </c>
       <c r="E4" t="n">
-        <v>854</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="5">
@@ -8132,16 +8132,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D9" t="n">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="E9" t="n">
-        <v>909</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10">
@@ -8208,16 +8208,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="D13" t="n">
-        <v>347</v>
+        <v>555</v>
       </c>
       <c r="E13" t="n">
-        <v>854</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="14">
@@ -8227,16 +8227,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>347</v>
+        <v>537</v>
       </c>
       <c r="E14" t="n">
-        <v>903</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="15">
@@ -8246,16 +8246,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C15" t="n">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="D15" t="n">
-        <v>352</v>
+        <v>583</v>
       </c>
       <c r="E15" t="n">
-        <v>1077</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="16">
@@ -8325,13 +8325,13 @@
         <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -8398,16 +8398,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C23" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D23" t="n">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="E23" t="n">
-        <v>909</v>
+        <v>861</v>
       </c>
     </row>
     <row r="24">
@@ -8417,16 +8417,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C24" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D24" t="n">
-        <v>393</v>
+        <v>310</v>
       </c>
       <c r="E24" t="n">
-        <v>896</v>
+        <v>853</v>
       </c>
     </row>
     <row r="25">
@@ -8436,16 +8436,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C25" t="n">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="D25" t="n">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="E25" t="n">
-        <v>1097</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="26">
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="D29" t="n">
-        <v>347</v>
+        <v>537</v>
       </c>
       <c r="E29" t="n">
-        <v>903</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="30">
@@ -8531,16 +8531,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C30" t="n">
-        <v>146</v>
+        <v>241</v>
       </c>
       <c r="D30" t="n">
-        <v>352</v>
+        <v>583</v>
       </c>
       <c r="E30" t="n">
-        <v>1077</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="31">
@@ -8550,16 +8550,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C31" t="n">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="D31" t="n">
-        <v>331</v>
+        <v>541</v>
       </c>
       <c r="E31" t="n">
-        <v>1111</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="32">
@@ -8588,16 +8588,16 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>21</v>
+      </c>
+      <c r="C33" t="n">
+        <v>28</v>
+      </c>
+      <c r="D33" t="n">
+        <v>29</v>
+      </c>
+      <c r="E33" t="n">
         <v>26</v>
-      </c>
-      <c r="C33" t="n">
-        <v>40</v>
-      </c>
-      <c r="D33" t="n">
-        <v>39</v>
-      </c>
-      <c r="E33" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -8648,13 +8648,13 @@
         <v>19</v>
       </c>
       <c r="C36" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -8664,16 +8664,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -8702,16 +8702,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C39" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D39" t="n">
-        <v>393</v>
+        <v>310</v>
       </c>
       <c r="E39" t="n">
-        <v>896</v>
+        <v>853</v>
       </c>
     </row>
     <row r="40">
@@ -8721,16 +8721,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C40" t="n">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="D40" t="n">
-        <v>429</v>
+        <v>489</v>
       </c>
       <c r="E40" t="n">
-        <v>1097</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="41">
@@ -8743,13 +8743,13 @@
         <v>95</v>
       </c>
       <c r="C41" t="n">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="D41" t="n">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E41" t="n">
-        <v>1054</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="42">
@@ -8778,16 +8778,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C43" t="n">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="D43" t="n">
-        <v>331</v>
+        <v>541</v>
       </c>
       <c r="E43" t="n">
-        <v>1111</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="44">
@@ -8797,16 +8797,16 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>21</v>
+      </c>
+      <c r="C44" t="n">
+        <v>28</v>
+      </c>
+      <c r="D44" t="n">
+        <v>29</v>
+      </c>
+      <c r="E44" t="n">
         <v>26</v>
-      </c>
-      <c r="C44" t="n">
-        <v>40</v>
-      </c>
-      <c r="D44" t="n">
-        <v>39</v>
-      </c>
-      <c r="E44" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -8816,16 +8816,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C45" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D45" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E45" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -8854,16 +8854,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -8876,13 +8876,13 @@
         <v>95</v>
       </c>
       <c r="C48" t="n">
-        <v>179</v>
+        <v>225</v>
       </c>
       <c r="D48" t="n">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E48" t="n">
-        <v>1054</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="49">
@@ -8892,16 +8892,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C49" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E49" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
